--- a/data/source.xlsx
+++ b/data/source.xlsx
@@ -481,16 +481,97 @@
   <s:si>
     <s:t>25.05.26 в 14:05</s:t>
   </s:si>
+  <s:si>
+    <s:t>Срок до </s:t>
+  </s:si>
+  <s:si>
+    <s:t>12-0342/2026
+Люблинский суд </s:t>
+  </s:si>
+  <s:si>
+    <s:t>16.03.2026 Вынесено решение о взыскании с ООО "ХардЭнерджи" 150 000 руб. 
+Будем подавать апеляшку ?</s:t>
+  </s:si>
+  <s:si>
+    <s:t>530986г32896</s:t>
+  </s:si>
+  <s:si>
+    <s:t>20.03.2026 в 19:10</s:t>
+  </s:si>
+  <s:si>
+    <s:t>20.03.2026 в 19:25</s:t>
+  </s:si>
+  <s:si>
+    <s:t>20.03.2026 в 19:20</s:t>
+  </s:si>
+  <s:si>
+    <s:t>САО РЕСО-Гарантия"</s:t>
+  </s:si>
+  <s:si>
+    <s:t>САО "РЕСО-Гарантия"</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Составить исковое заявление.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Составить исковое заявление</s:t>
+  </s:si>
+  <s:si>
+    <s:t>20.03.2026 в 19:22</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Сделать экспертизу авто.
+Составить исковое заявление</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Взысканиие арендых платежей. Иск рассмотрели, в порядке упращенки удовлетворили. Подали апеляцию на краткое решение. Гриф представил аозражение на жалобу.
+Отслеживаем статус </s:t>
+  </s:si>
+  <s:si>
+    <s:t>16.03.2026 Вынесено решение о взыскании с ООО "ХардЭнерджи" 150 000 руб. 
+Ждем решение на Гос услуги
+Будем подавать апеляшку ?</s:t>
+  </s:si>
+  <s:si>
+    <s:t>16.03.2026 Вынесено решение о взыскании с ООО "ХардЭнерджи" 150 000 руб. 
+Ждем Решение на Гос услуги
+Будем подавать апеляшку ?</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Возмещение по ДТП порядка 2 000 000. скостили до 300 000 по экспертизе. Во первых есть водитель с него взыскать. 
+Дождаться решения первой инстанции. Машина продана отцу истца, оценить ущерб. Они ссылась на ходовую часть автомобиля которая не подвердилась.
+04.02.26 иск удовлетворен частитчно, будем подавать апеляцию ? + отлеживаем поступление апеляшки от аппонентов</s:t>
+  </s:si>
+  <s:si>
+    <s:t>20.03.2026 в 19:30</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Превлечь директора к субсидиарке.
+Есть ИНН организации ?</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Просят индексацию на 28 000.
+Просто отсдеживаем </s:t>
+  </s:si>
+  <s:si>
+    <s:t>20.03.2026 в 19:35</s:t>
+  </s:si>
+  <s:si>
+    <s:t>20.03.2026 в 19:40</s:t>
+  </s:si>
+  <s:si>
+    <s:t>20.03.2026 в 19:50</s:t>
+  </s:si>
 </s:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<s:styleSheet xmlns:vyd="http://volga.yandex.com/schemas/document/model" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<s:styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:vyd="http://volga.yandex.com/schemas/document/model" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <s:numFmts count="2">
     <s:numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
     <s:numFmt numFmtId="165" formatCode="dd\.mm\.yy"/>
   </s:numFmts>
-  <s:fonts count="3">
+  <s:fonts count="4">
     <s:font>
       <s:name val="Arial"/>
       <s:family val="2"/>
@@ -503,6 +584,13 @@
     <s:font>
       <s:name val="Times New Roman"/>
       <s:b val="1"/>
+    </s:font>
+    <s:font>
+      <s:name val="Arial"/>
+      <s:family val="2"/>
+      <s:b val="1"/>
+      <s:color theme="1"/>
+      <s:sz val="10"/>
     </s:font>
   </s:fonts>
   <s:fills count="8">
@@ -619,7 +707,7 @@
   <s:cellStyleXfs count="1">
     <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </s:cellStyleXfs>
-  <s:cellXfs count="69">
+  <s:cellXfs count="76">
     <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <s:xf applyAlignment="1">
       <s:alignment vertical="center" mc:Ignorable="vyd"/>
@@ -786,6 +874,21 @@
     </s:xf>
     <s:xf numFmtId="165" fillId="7" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <s:alignment horizontal="center" vertical="center" wrapText="1" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <s:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <s:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="165" borderId="1" applyNumberFormat="1" applyBorder="1"/>
+    <s:xf numFmtId="165" borderId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <s:alignment vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf borderId="1" applyBorder="1" applyAlignment="1">
+      <s:alignment vertical="center" mc:Ignorable="vyd"/>
     </s:xf>
   </s:cellXfs>
   <s:cellStyles count="1">
@@ -4713,7 +4816,7 @@
     <s:col min="3" max="3" width="28.051" customWidth="1"/>
     <s:col min="4" max="4" width="21.98" customWidth="1"/>
     <s:col min="5" max="5" width="48.293" customWidth="1"/>
-    <s:col min="6" max="6" width="56.383" customWidth="1"/>
+    <s:col min="6" max="6" width="10.922" style="2" customWidth="1"/>
   </s:cols>
   <s:sheetData>
     <s:row r="1">
@@ -4732,6 +4835,9 @@
       <s:c r="E1" s="37" t="s">
         <s:v>4</s:v>
       </s:c>
+      <s:c r="F1" s="37" t="s">
+        <s:v>136</s:v>
+      </s:c>
     </s:row>
     <s:row r="2" ht="110.25">
       <s:c r="A2" s="35" t="s">
@@ -4749,6 +4855,9 @@
       <s:c r="E2" s="35" t="s">
         <s:v>92</s:v>
       </s:c>
+      <s:c r="F2" s="51">
+        <s:v>46108</s:v>
+      </s:c>
     </s:row>
     <s:row r="3" ht="146.25">
       <s:c r="A3" s="35" t="s">
@@ -4766,6 +4875,9 @@
       <s:c r="E3" s="35" t="s">
         <s:v>86</s:v>
       </s:c>
+      <s:c r="F3" s="51">
+        <s:v>46104</s:v>
+      </s:c>
     </s:row>
     <s:row r="4" ht="110.25">
       <s:c r="A4" s="35" t="s">
@@ -4783,6 +4895,9 @@
       <s:c r="E4" s="35" t="s">
         <s:v>123</s:v>
       </s:c>
+      <s:c r="F4" s="51">
+        <s:v>46104</s:v>
+      </s:c>
     </s:row>
     <s:row r="5" ht="38.25">
       <s:c r="A5" s="35" t="s">
@@ -4800,6 +4915,7 @@
       <s:c r="E5" s="35" t="s">
         <s:v>90</s:v>
       </s:c>
+      <s:c r="F5" s="3"/>
     </s:row>
     <s:row r="6" ht="26.25">
       <s:c r="A6" s="35" t="s">
@@ -4815,8 +4931,9 @@
         <s:v>46</s:v>
       </s:c>
       <s:c r="E6" s="35" t="s">
-        <s:v>94</s:v>
-      </s:c>
+        <s:v>155</s:v>
+      </s:c>
+      <s:c r="F6" s="3"/>
       <s:c r="G6"/>
     </s:row>
     <s:row r="7" ht="62.25">
@@ -4835,8 +4952,11 @@
       <s:c r="E7" s="35" t="s">
         <s:v>76</s:v>
       </s:c>
-    </s:row>
-    <s:row r="8" ht="62.25">
+      <s:c r="F7" s="51">
+        <s:v>46160</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="8" ht="98.25">
       <s:c r="A8" s="35" t="s">
         <s:v>95</s:v>
       </s:c>
@@ -4848,12 +4968,15 @@
       </s:c>
       <s:c r="D8" s="35"/>
       <s:c r="E8" s="35" t="s">
-        <s:v>98</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="9" ht="38.25">
+        <s:v>152</s:v>
+      </s:c>
+      <s:c r="F8" s="51">
+        <s:v>46104</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="9" ht="50.25">
       <s:c r="A9" s="35" t="s">
-        <s:v>99</s:v>
+        <s:v>137</s:v>
       </s:c>
       <s:c r="B9" s="35" t="s">
         <s:v>45</s:v>
@@ -4863,7 +4986,10 @@
         <s:v>101</s:v>
       </s:c>
       <s:c r="E9" s="35" t="s">
-        <s:v>132</s:v>
+        <s:v>151</s:v>
+      </s:c>
+      <s:c r="F9" s="51">
+        <s:v>46104</s:v>
       </s:c>
     </s:row>
     <s:row r="10" ht="26.25">
@@ -4881,6 +5007,9 @@
       </s:c>
       <s:c r="E10" s="35" t="s">
         <s:v>111</s:v>
+      </s:c>
+      <s:c r="F10" s="51">
+        <s:v>46111</s:v>
       </s:c>
     </s:row>
     <s:row r="11">
@@ -4893,6 +5022,7 @@
       <s:c r="E11" s="35" t="s">
         <s:v>118</s:v>
       </s:c>
+      <s:c r="F11" s="3"/>
     </s:row>
     <s:row r="12">
       <s:c r="A12" s="35"/>
@@ -4904,8 +5034,9 @@
       <s:c r="E12" s="35" t="s">
         <s:v>117</s:v>
       </s:c>
-    </s:row>
-    <s:row r="13" ht="38.25">
+      <s:c r="F12" s="3"/>
+    </s:row>
+    <s:row r="13" ht="50.25">
       <s:c r="A13" s="35" t="s">
         <s:v>119</s:v>
       </s:c>
@@ -4917,10 +5048,13 @@
       </s:c>
       <s:c r="D13" s="35"/>
       <s:c r="E13" s="35" t="s">
-        <s:v>121</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="14">
+        <s:v>149</s:v>
+      </s:c>
+      <s:c r="F13" s="51">
+        <s:v>46104</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="14" ht="26.25">
       <s:c r="A14" s="35"/>
       <s:c r="B14" s="35" t="s">
         <s:v>45</s:v>
@@ -4930,15 +5064,27 @@
       </s:c>
       <s:c r="D14" s="35"/>
       <s:c r="E14" s="35" t="s">
+        <s:v>154</s:v>
+      </s:c>
+      <s:c r="F14" s="3"/>
+    </s:row>
+    <s:row r="15">
+      <s:c r="A15" s="35" t="s">
+        <s:v>139</s:v>
+      </s:c>
+      <s:c r="B15" s="35">
+        <s:v>25535</s:v>
+      </s:c>
+      <s:c r="C15" s="35">
+        <s:v>57373645</s:v>
+      </s:c>
+      <s:c r="D15" s="35" t="s">
+        <s:v>158</s:v>
+      </s:c>
+      <s:c r="E15" s="35" t="s">
         <s:v>126</s:v>
       </s:c>
-    </s:row>
-    <s:row r="15">
-      <s:c r="A15" s="35"/>
-      <s:c r="B15" s="35"/>
-      <s:c r="C15" s="35"/>
-      <s:c r="D15" s="35"/>
-      <s:c r="E15" s="35"/>
+      <s:c r="F15" s="3"/>
     </s:row>
     <s:row r="16">
       <s:c r="A16" s="35"/>
@@ -4946,6 +5092,7 @@
       <s:c r="C16" s="35"/>
       <s:c r="D16" s="35"/>
       <s:c r="E16" s="35"/>
+      <s:c r="F16" s="3"/>
     </s:row>
     <s:row r="17">
       <s:c r="A17" s="35"/>
@@ -4953,6 +5100,7 @@
       <s:c r="C17" s="35"/>
       <s:c r="D17" s="35"/>
       <s:c r="E17" s="35"/>
+      <s:c r="F17" s="3"/>
     </s:row>
     <s:row r="18">
       <s:c r="A18" s="35"/>
@@ -4960,6 +5108,7 @@
       <s:c r="C18" s="35"/>
       <s:c r="D18" s="35"/>
       <s:c r="E18" s="35"/>
+      <s:c r="F18" s="3"/>
     </s:row>
     <s:row r="19">
       <s:c r="A19" s="35"/>
@@ -4967,6 +5116,7 @@
       <s:c r="C19" s="35"/>
       <s:c r="D19" s="35"/>
       <s:c r="E19" s="35"/>
+      <s:c r="F19" s="3"/>
     </s:row>
     <s:row r="20">
       <s:c r="A20" s="35"/>
@@ -4974,6 +5124,7 @@
       <s:c r="C20" s="35"/>
       <s:c r="D20" s="35"/>
       <s:c r="E20" s="35"/>
+      <s:c r="F20" s="3"/>
     </s:row>
     <s:row r="21">
       <s:c r="A21" s="35"/>
@@ -4981,6 +5132,7 @@
       <s:c r="C21" s="35"/>
       <s:c r="D21" s="35"/>
       <s:c r="E21" s="35"/>
+      <s:c r="F21" s="3"/>
     </s:row>
     <s:row r="22">
       <s:c r="A22" s="35"/>
@@ -4988,6 +5140,7 @@
       <s:c r="C22" s="35"/>
       <s:c r="D22" s="35"/>
       <s:c r="E22" s="35"/>
+      <s:c r="F22" s="3"/>
     </s:row>
     <s:row r="23">
       <s:c r="A23" s="35"/>
@@ -4995,6 +5148,7 @@
       <s:c r="C23" s="35"/>
       <s:c r="D23" s="35"/>
       <s:c r="E23" s="35"/>
+      <s:c r="F23" s="3"/>
     </s:row>
     <s:row r="24">
       <s:c r="A24" s="35"/>
@@ -5002,6 +5156,7 @@
       <s:c r="C24" s="35"/>
       <s:c r="D24" s="35"/>
       <s:c r="E24" s="35"/>
+      <s:c r="F24" s="3"/>
     </s:row>
     <s:row r="25">
       <s:c r="A25" s="35"/>
@@ -5009,6 +5164,7 @@
       <s:c r="C25" s="35"/>
       <s:c r="D25" s="35"/>
       <s:c r="E25" s="35"/>
+      <s:c r="F25" s="3"/>
     </s:row>
     <s:row r="26">
       <s:c r="A26" s="35"/>
@@ -5016,6 +5172,7 @@
       <s:c r="C26" s="35"/>
       <s:c r="D26" s="35"/>
       <s:c r="E26" s="35"/>
+      <s:c r="F26" s="3"/>
     </s:row>
     <s:row r="27">
       <s:c r="A27" s="35"/>
@@ -5023,6 +5180,7 @@
       <s:c r="C27" s="35"/>
       <s:c r="D27" s="35"/>
       <s:c r="E27" s="35"/>
+      <s:c r="F27" s="3"/>
     </s:row>
     <s:row r="28">
       <s:c r="A28" s="35"/>
@@ -5030,6 +5188,7 @@
       <s:c r="C28" s="35"/>
       <s:c r="D28" s="35"/>
       <s:c r="E28" s="35"/>
+      <s:c r="F28" s="3"/>
     </s:row>
     <s:row r="29">
       <s:c r="A29" s="35"/>
@@ -5037,6 +5196,7 @@
       <s:c r="C29" s="35"/>
       <s:c r="D29" s="35"/>
       <s:c r="E29" s="35"/>
+      <s:c r="F29" s="3"/>
     </s:row>
     <s:row r="30">
       <s:c r="A30" s="35"/>
@@ -5044,6 +5204,7 @@
       <s:c r="C30" s="35"/>
       <s:c r="D30" s="35"/>
       <s:c r="E30" s="35"/>
+      <s:c r="F30" s="3"/>
     </s:row>
     <s:row r="31">
       <s:c r="A31" s="35"/>
@@ -5051,6 +5212,7 @@
       <s:c r="C31" s="35"/>
       <s:c r="D31" s="35"/>
       <s:c r="E31" s="35"/>
+      <s:c r="F31" s="3"/>
     </s:row>
     <s:row r="38">
       <s:c r="A38" s="40" t="s">
@@ -5100,10 +5262,16 @@
       <s:c r="D41" s="48"/>
       <s:c r="E41" s="48"/>
     </s:row>
-    <s:row r="42">
-      <s:c r="A42" s="36"/>
-      <s:c r="B42" s="36"/>
-      <s:c r="C42" s="36"/>
+    <s:row r="42" ht="26.25">
+      <s:c r="A42" s="36" t="s">
+        <s:v>36</s:v>
+      </s:c>
+      <s:c r="B42" s="36" t="s">
+        <s:v>144</s:v>
+      </s:c>
+      <s:c r="C42" s="36" t="s">
+        <s:v>148</s:v>
+      </s:c>
     </s:row>
     <s:row r="43">
       <s:c r="A43" s="36"/>

--- a/data/source.xlsx
+++ b/data/source.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<s:workbook xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <s:workbookPr/>
   <s:bookViews>
     <s:workbookView xWindow="3160" yWindow="2260" windowWidth="28240" windowHeight="17240"/>
@@ -562,11 +562,123 @@
   <s:si>
     <s:t>20.03.2026 в 19:50</s:t>
   </s:si>
+  <s:si>
+    <s:t xml:space="preserve">В удовлетворении заявлени о привлечении Кидяевой А.Г. отказано.
+Ждем мотивировочную часть. ИСк удовлетворен. 
+Оспаривать на основании непривлечения в качестве третьего лица. В процессе заявили ходатайство о привлечении. 
+Иск об оспаривании сделки не подавалисся. 
+Мысли: Гурьянова-Теплорост не оспорить по основаниям приемущественного права. Либо безденежность, не было денег.  
+По этому делу Кидяева обращалась к Гурьяновой и Теплорост. 
+Планировалось дождаться решения по проверке в УВД. 
+По состоянию на 23.03.2026 мотивировочной части нету </s:t>
+  </s:si>
+  <s:si>
+    <s:t>18.02.2026 приостановленно рассмотрение АЖ.
+Назначена экспертиза, в первой инстанции говорят что отказано, а в решении Написано что не заявлялось. 
+По состоянию на 23.03.26 заключение экмпертов в суд не поступило</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Просят индексацию на 28 000.
+Просто отсдеживаем.
+22.01.26 от ДДС Авто поступило объяснение</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Возмещение по ДТП порядка 2 000 000. скостили до 300 000 по экспертизе. Во первых есть водитель с него взыскать. 
+Дождаться решения первой инстанции. Машина продана отцу истца, оценить ущерб. Они ссылась на ходовую часть автомобиля которая не подвердилась.
+04.02.26 иск удовлетворен частитчно, будем подавать апеляцию ? + отлеживаем поступление апеляшки от аппонентов.
+По состоянию на 23.03.26 АЖ не поступила</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">Взысканиие арендых платежей. Иск рассмотрели, в порядке упращенки удовлетворили. Подали апеляцию на краткое решение. Гриф представил аозражение на жалобу.
+Отслеживаем статус.
+19.03.26 в удовлетворении АЖ отказано. На обжалование 2 месяца </s:t>
+  </s:si>
+  <s:si>
+    <s:t>Взысканиие арендых платежей. Иск рассмотрели, в порядке упращенки удовлетворили. Подали апеляцию на краткое решение. Гриф представил аозражение на жалобу.
+Отслеживаем статус.
+19.03.26 в удовлетворении АЖ отказано. На обжалование 2 месяца.</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">Взысканиие арендых платежей. Иск рассмотрели, в порядке упращенки удовлетворили. Подали апеляцию на краткое решение. Гриф представил аозражение на жалобу.
+Отслеживаем статус.
+19.03.26 в удовлетворении АЖ отказано. На обжалование 2 месяца.
+Подаем кассационную жалобу ? </s:t>
+  </s:si>
+  <s:si>
+    <s:t>16.03.2026 Вынесено решение о взыскании с ООО "ХардЭнерджи" 150 000 руб. 
+Ждем Решение на Гос услуги
+По состоянию на 23.03.26 Решение не опубликовано,
+Будем подавать апеляшку ?</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">В удовлетворении заявлени о привлечении Кидяевой А.Г. отказано.
+Ждем мотивировочную часть. Иск удовлетворен. 
+Оспаривать на основании непривлечения в качестве третьего лица. В процессе заявили ходатайство о привлечении. 
+Иск об оспаривании сделки не подавалисся. 
+Мысли: Гурьянова-Теплорост не оспорить по основаниям приемущественного права. Либо безденежность, не было денег.  
+По этому делу Кидяева обращалась к Гурьяновой и Теплорост. 
+Планировалось дождаться решения по проверке в УВД. 
+По состоянию на 23.03.2026 мотивировочной части нету </s:t>
+  </s:si>
+  <s:si>
+    <s:t>Избрание председателя совета директоров</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Анализ договора БТЛ</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">Договор отредактирован и направлен Ивану. </s:t>
+  </s:si>
+  <s:si>
+    <s:t>Уведомление о расторжении договора с Нетунаевым</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Подготовлено уведомление. В формате ПДФ направлено Ивану для отправки с официальной почты организации.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Ходатайство о возврате ДС 80 000 с депозитного счета суда</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">Ходатайство подготовлено. Необходимо вписать реквизиты счета получателя и можно направлять в суд. </s:t>
+  </s:si>
+  <s:si>
+    <s:t>Составление искового заявление о взыскании ДС с Композиции</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">Исковое заявление написано. Необходимо оплатить госпошлину и отправить стороне копию иска. После можно направлять в суд. </s:t>
+  </s:si>
+  <s:si>
+    <s:t>Оплата счет БК</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">Напомнить Жене оплатить счет. </s:t>
+  </s:si>
+  <s:si>
+    <s:t>Возврат стеллы БК</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Тендер на строительство защитного ограждения Росгидро</s:t>
+  </s:si>
+  <s:si>
+    <s:t>КП предоставлено в адрес Заказчика. Необходимо 27.03.2026 набрать ему и уточнить статус. Когда будет решение по тендеру ?</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Подписани ИД МИСК</s:t>
+  </s:si>
+  <s:si>
+    <s:t>24.03.2026 передано ИД на подписание Заказчику по договору № 303/8-24 от 12.07.23</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">24.03.2026 передано ИД на подписание Заказчику по договору № 303/8-24 от 12.07.23. 26.03.26 Нас ожидают со второй частью ИД </s:t>
+  </s:si>
+  <s:si>
+    <s:t>отовлю решение. Составляю осталось составить повестку дня</s:t>
+  </s:si>
 </s:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<s:styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:vyd="http://volga.yandex.com/schemas/document/model" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<s:styleSheet xmlns:vyd="http://volga.yandex.com/schemas/document/model" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <s:numFmts count="2">
     <s:numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
     <s:numFmt numFmtId="165" formatCode="dd\.mm\.yy"/>
@@ -593,7 +705,7 @@
       <s:sz val="10"/>
     </s:font>
   </s:fonts>
-  <s:fills count="8">
+  <s:fills count="12">
     <s:fill>
       <s:patternFill patternType="none"/>
     </s:fill>
@@ -634,6 +746,30 @@
       <s:patternFill patternType="solid">
         <s:fgColor rgb="FF7EDD9C"/>
         <s:bgColor rgb="FF7EDD9C"/>
+      </s:patternFill>
+    </s:fill>
+    <s:fill>
+      <s:patternFill patternType="solid">
+        <s:fgColor rgb="FFFFE45C"/>
+        <s:bgColor rgb="FFFFE45C"/>
+      </s:patternFill>
+    </s:fill>
+    <s:fill>
+      <s:patternFill patternType="solid">
+        <s:fgColor rgb="FFFF8800"/>
+        <s:bgColor rgb="FFFF8800"/>
+      </s:patternFill>
+    </s:fill>
+    <s:fill>
+      <s:patternFill patternType="solid">
+        <s:fgColor rgb="FF4DA0FF"/>
+        <s:bgColor rgb="FF4DA0FF"/>
+      </s:patternFill>
+    </s:fill>
+    <s:fill>
+      <s:patternFill patternType="solid">
+        <s:fgColor rgb="FFFF6964"/>
+        <s:bgColor rgb="FFFF6964"/>
       </s:patternFill>
     </s:fill>
   </s:fills>
@@ -707,7 +843,7 @@
   <s:cellStyleXfs count="1">
     <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </s:cellStyleXfs>
-  <s:cellXfs count="76">
+  <s:cellXfs count="90">
     <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <s:xf applyAlignment="1">
       <s:alignment vertical="center" mc:Ignorable="vyd"/>
@@ -889,6 +1025,44 @@
     </s:xf>
     <s:xf borderId="1" applyBorder="1" applyAlignment="1">
       <s:alignment vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="1" fillId="8" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="1" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="165" fillId="8" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="2" fillId="3" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="1" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="2" fillId="9" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="1" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fillId="10" borderId="1" applyFill="1" applyBorder="1"/>
+    <s:xf fillId="10" borderId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="1" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fillId="5" borderId="1" applyFill="1" applyBorder="1"/>
+    <s:xf numFmtId="0" fillId="5" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="1" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="1" fillId="6" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="1" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="1" fillId="6" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="165" fillId="6" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="1" fillId="11" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="1" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="1" fillId="11" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="165" fillId="11" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" mc:Ignorable="vyd"/>
     </s:xf>
   </s:cellXfs>
   <s:cellStyles count="1">
@@ -1122,68 +1296,54 @@
       <s:c r="G1" s="2"/>
     </s:row>
     <s:row r="2" ht="24.75">
-      <s:c r="A2" s="59">
-        <s:v>1</s:v>
-      </s:c>
+      <s:c r="A2" s="59"/>
       <s:c r="B2" s="59" t="s">
-        <s:v>5</s:v>
-      </s:c>
-      <s:c r="C2" s="60">
-        <s:v>46086</s:v>
-      </s:c>
-      <s:c r="D2" s="61">
-        <s:v>46098</s:v>
-      </s:c>
-      <s:c r="E2" s="59" t="s">
-        <s:v>128</s:v>
-      </s:c>
+        <s:v>168</s:v>
+      </s:c>
+      <s:c r="C2" s="60"/>
+      <s:c r="D2" s="61"/>
+      <s:c r="E2" s="59"/>
       <s:c r="F2" s="2"/>
       <s:c r="G2" s="2"/>
     </s:row>
-    <s:row r="3" ht="36">
-      <s:c r="A3" s="6">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="B3" s="6" t="s">
-        <s:v>6</s:v>
-      </s:c>
-      <s:c r="C3" s="14">
-        <s:v>46086</s:v>
-      </s:c>
-      <s:c r="D3" s="51">
-        <s:v>46099</s:v>
-      </s:c>
-      <s:c r="E3" s="6" t="s">
-        <s:v>130</s:v>
+    <s:row r="3" ht="24.75">
+      <s:c r="A3" s="59"/>
+      <s:c r="B3" s="59" t="s">
+        <s:v>5</s:v>
+      </s:c>
+      <s:c r="C3" s="60"/>
+      <s:c r="D3" s="61"/>
+      <s:c r="E3" s="83" t="s">
+        <s:v>185</s:v>
       </s:c>
       <s:c r="F3" s="2"/>
       <s:c r="G3" s="2"/>
     </s:row>
-    <s:row r="4">
-      <s:c r="A4" s="6">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="B4" s="6"/>
-      <s:c r="C4" s="3"/>
-      <s:c r="D4" s="3"/>
-      <s:c r="E4" s="6"/>
+    <s:row r="4" ht="36">
+      <s:c r="A4" s="59"/>
+      <s:c r="B4" s="83" t="s">
+        <s:v>6</s:v>
+      </s:c>
+      <s:c r="C4" s="60"/>
+      <s:c r="D4" s="61"/>
+      <s:c r="E4" s="59" t="s">
+        <s:v>130</s:v>
+      </s:c>
       <s:c r="F4" s="2"/>
       <s:c r="G4" s="2"/>
     </s:row>
-    <s:row r="5">
-      <s:c r="A5" s="6">
-        <s:v>4</s:v>
-      </s:c>
+    <s:row r="5" ht="14.25">
+      <s:c r="A5" s="6"/>
       <s:c r="B5" s="6"/>
-      <s:c r="C5" s="3"/>
-      <s:c r="D5" s="3"/>
+      <s:c r="C5" s="14"/>
+      <s:c r="D5" s="51"/>
       <s:c r="E5" s="6"/>
       <s:c r="F5" s="2"/>
       <s:c r="G5" s="2"/>
     </s:row>
     <s:row r="6">
       <s:c r="A6" s="6">
-        <s:v>5</s:v>
+        <s:v>3</s:v>
       </s:c>
       <s:c r="B6" s="6"/>
       <s:c r="C6" s="3"/>
@@ -1192,9 +1352,9 @@
       <s:c r="F6" s="2"/>
       <s:c r="G6" s="2"/>
     </s:row>
-    <s:row r="7" ht="12.75" customHeight="1">
+    <s:row r="7">
       <s:c r="A7" s="6">
-        <s:v>6</s:v>
+        <s:v>4</s:v>
       </s:c>
       <s:c r="B7" s="6"/>
       <s:c r="C7" s="3"/>
@@ -1205,7 +1365,7 @@
     </s:row>
     <s:row r="8">
       <s:c r="A8" s="6">
-        <s:v>7</s:v>
+        <s:v>5</s:v>
       </s:c>
       <s:c r="B8" s="6"/>
       <s:c r="C8" s="3"/>
@@ -1214,9 +1374,9 @@
       <s:c r="F8" s="2"/>
       <s:c r="G8" s="2"/>
     </s:row>
-    <s:row r="9">
+    <s:row r="9" ht="12.75" customHeight="1">
       <s:c r="A9" s="6">
-        <s:v>8</s:v>
+        <s:v>6</s:v>
       </s:c>
       <s:c r="B9" s="6"/>
       <s:c r="C9" s="3"/>
@@ -1227,7 +1387,7 @@
     </s:row>
     <s:row r="10">
       <s:c r="A10" s="6">
-        <s:v>9</s:v>
+        <s:v>7</s:v>
       </s:c>
       <s:c r="B10" s="6"/>
       <s:c r="C10" s="3"/>
@@ -1238,7 +1398,7 @@
     </s:row>
     <s:row r="11">
       <s:c r="A11" s="6">
-        <s:v>10</s:v>
+        <s:v>8</s:v>
       </s:c>
       <s:c r="B11" s="6"/>
       <s:c r="C11" s="3"/>
@@ -1249,7 +1409,7 @@
     </s:row>
     <s:row r="12">
       <s:c r="A12" s="6">
-        <s:v>11</s:v>
+        <s:v>9</s:v>
       </s:c>
       <s:c r="B12" s="6"/>
       <s:c r="C12" s="3"/>
@@ -1260,7 +1420,7 @@
     </s:row>
     <s:row r="13">
       <s:c r="A13" s="6">
-        <s:v>12</s:v>
+        <s:v>10</s:v>
       </s:c>
       <s:c r="B13" s="6"/>
       <s:c r="C13" s="3"/>
@@ -1271,7 +1431,7 @@
     </s:row>
     <s:row r="14">
       <s:c r="A14" s="6">
-        <s:v>13</s:v>
+        <s:v>11</s:v>
       </s:c>
       <s:c r="B14" s="6"/>
       <s:c r="C14" s="3"/>
@@ -1282,7 +1442,7 @@
     </s:row>
     <s:row r="15">
       <s:c r="A15" s="6">
-        <s:v>14</s:v>
+        <s:v>12</s:v>
       </s:c>
       <s:c r="B15" s="6"/>
       <s:c r="C15" s="3"/>
@@ -1293,7 +1453,7 @@
     </s:row>
     <s:row r="16">
       <s:c r="A16" s="6">
-        <s:v>15</s:v>
+        <s:v>13</s:v>
       </s:c>
       <s:c r="B16" s="6"/>
       <s:c r="C16" s="3"/>
@@ -1304,7 +1464,7 @@
     </s:row>
     <s:row r="17">
       <s:c r="A17" s="6">
-        <s:v>16</s:v>
+        <s:v>14</s:v>
       </s:c>
       <s:c r="B17" s="6"/>
       <s:c r="C17" s="3"/>
@@ -1315,7 +1475,7 @@
     </s:row>
     <s:row r="18">
       <s:c r="A18" s="6">
-        <s:v>17</s:v>
+        <s:v>15</s:v>
       </s:c>
       <s:c r="B18" s="6"/>
       <s:c r="C18" s="3"/>
@@ -1326,7 +1486,7 @@
     </s:row>
     <s:row r="19">
       <s:c r="A19" s="6">
-        <s:v>18</s:v>
+        <s:v>16</s:v>
       </s:c>
       <s:c r="B19" s="6"/>
       <s:c r="C19" s="3"/>
@@ -1337,7 +1497,7 @@
     </s:row>
     <s:row r="20">
       <s:c r="A20" s="6">
-        <s:v>19</s:v>
+        <s:v>17</s:v>
       </s:c>
       <s:c r="B20" s="6"/>
       <s:c r="C20" s="3"/>
@@ -1348,7 +1508,7 @@
     </s:row>
     <s:row r="21">
       <s:c r="A21" s="6">
-        <s:v>20</s:v>
+        <s:v>18</s:v>
       </s:c>
       <s:c r="B21" s="6"/>
       <s:c r="C21" s="3"/>
@@ -1359,7 +1519,7 @@
     </s:row>
     <s:row r="22">
       <s:c r="A22" s="6">
-        <s:v>21</s:v>
+        <s:v>19</s:v>
       </s:c>
       <s:c r="B22" s="6"/>
       <s:c r="C22" s="3"/>
@@ -1370,7 +1530,7 @@
     </s:row>
     <s:row r="23">
       <s:c r="A23" s="6">
-        <s:v>22</s:v>
+        <s:v>20</s:v>
       </s:c>
       <s:c r="B23" s="6"/>
       <s:c r="C23" s="3"/>
@@ -1381,7 +1541,7 @@
     </s:row>
     <s:row r="24">
       <s:c r="A24" s="6">
-        <s:v>23</s:v>
+        <s:v>21</s:v>
       </s:c>
       <s:c r="B24" s="6"/>
       <s:c r="C24" s="3"/>
@@ -1392,7 +1552,7 @@
     </s:row>
     <s:row r="25">
       <s:c r="A25" s="6">
-        <s:v>24</s:v>
+        <s:v>22</s:v>
       </s:c>
       <s:c r="B25" s="6"/>
       <s:c r="C25" s="3"/>
@@ -1403,7 +1563,7 @@
     </s:row>
     <s:row r="26">
       <s:c r="A26" s="6">
-        <s:v>25</s:v>
+        <s:v>23</s:v>
       </s:c>
       <s:c r="B26" s="6"/>
       <s:c r="C26" s="3"/>
@@ -1413,20 +1573,24 @@
       <s:c r="G26" s="2"/>
     </s:row>
     <s:row r="27">
-      <s:c r="A27" s="15"/>
-      <s:c r="B27" s="15"/>
-      <s:c r="C27" s="2"/>
-      <s:c r="D27" s="2"/>
-      <s:c r="E27" s="15"/>
+      <s:c r="A27" s="6">
+        <s:v>24</s:v>
+      </s:c>
+      <s:c r="B27" s="6"/>
+      <s:c r="C27" s="3"/>
+      <s:c r="D27" s="3"/>
+      <s:c r="E27" s="6"/>
       <s:c r="F27" s="2"/>
       <s:c r="G27" s="2"/>
     </s:row>
     <s:row r="28">
-      <s:c r="A28" s="15"/>
-      <s:c r="B28" s="15"/>
-      <s:c r="C28" s="2"/>
-      <s:c r="D28" s="2"/>
-      <s:c r="E28" s="15"/>
+      <s:c r="A28" s="6">
+        <s:v>25</s:v>
+      </s:c>
+      <s:c r="B28" s="6"/>
+      <s:c r="C28" s="3"/>
+      <s:c r="D28" s="3"/>
+      <s:c r="E28" s="6"/>
       <s:c r="F28" s="2"/>
       <s:c r="G28" s="2"/>
     </s:row>
@@ -1683,10 +1847,22 @@
       <s:c r="G56" s="2"/>
     </s:row>
     <s:row r="57">
-      <s:c r="A57" s="8"/>
+      <s:c r="A57" s="15"/>
+      <s:c r="B57" s="15"/>
+      <s:c r="C57" s="2"/>
+      <s:c r="D57" s="2"/>
+      <s:c r="E57" s="15"/>
+      <s:c r="F57" s="2"/>
+      <s:c r="G57" s="2"/>
     </s:row>
     <s:row r="58">
-      <s:c r="A58" s="8"/>
+      <s:c r="A58" s="15"/>
+      <s:c r="B58" s="15"/>
+      <s:c r="C58" s="2"/>
+      <s:c r="D58" s="2"/>
+      <s:c r="E58" s="15"/>
+      <s:c r="F58" s="2"/>
+      <s:c r="G58" s="2"/>
     </s:row>
     <s:row r="59">
       <s:c r="A59" s="8"/>
@@ -4513,6 +4689,12 @@
     </s:row>
     <s:row r="1000">
       <s:c r="A1000" s="8"/>
+    </s:row>
+    <s:row r="1001">
+      <s:c r="A1001" s="8"/>
+    </s:row>
+    <s:row r="1002">
+      <s:c r="A1002" s="8"/>
     </s:row>
   </s:sheetData>
 </s:worksheet>
@@ -4612,68 +4794,96 @@
         <s:v>130</s:v>
       </s:c>
     </s:row>
-    <s:row r="6">
-      <s:c r="A6" s="4">
+    <s:row r="6" ht="24.75">
+      <s:c r="A6" s="82">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="B6" s="6"/>
-      <s:c r="C6" s="6"/>
-      <s:c r="D6" s="6"/>
-      <s:c r="E6" s="6"/>
-    </s:row>
-    <s:row r="7">
-      <s:c r="A7" s="4">
+      <s:c r="B6" s="59" t="s">
+        <s:v>169</s:v>
+      </s:c>
+      <s:c r="C6" s="59"/>
+      <s:c r="D6" s="59"/>
+      <s:c r="E6" s="59" t="s">
+        <s:v>170</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="7" ht="47.25">
+      <s:c r="A7" s="56">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="B7" s="6"/>
-      <s:c r="C7" s="6"/>
-      <s:c r="D7" s="6"/>
-      <s:c r="E7" s="6"/>
-    </s:row>
-    <s:row r="8">
-      <s:c r="A8" s="4">
+      <s:c r="B7" s="57" t="s">
+        <s:v>171</s:v>
+      </s:c>
+      <s:c r="C7" s="57"/>
+      <s:c r="D7" s="57"/>
+      <s:c r="E7" s="57" t="s">
+        <s:v>172</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="8" ht="47.25">
+      <s:c r="A8" s="82">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="B8" s="6"/>
-      <s:c r="C8" s="6"/>
-      <s:c r="D8" s="6"/>
-      <s:c r="E8" s="6"/>
-    </s:row>
-    <s:row r="9">
-      <s:c r="A9" s="4">
+      <s:c r="B8" s="59" t="s">
+        <s:v>173</s:v>
+      </s:c>
+      <s:c r="C8" s="59"/>
+      <s:c r="D8" s="59"/>
+      <s:c r="E8" s="59" t="s">
+        <s:v>174</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="9" ht="58.5">
+      <s:c r="A9" s="82">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="B9" s="6"/>
-      <s:c r="C9" s="6"/>
-      <s:c r="D9" s="6"/>
-      <s:c r="E9" s="6"/>
-    </s:row>
-    <s:row r="10">
-      <s:c r="A10" s="4">
+      <s:c r="B9" s="59" t="s">
+        <s:v>175</s:v>
+      </s:c>
+      <s:c r="C9" s="59"/>
+      <s:c r="D9" s="59"/>
+      <s:c r="E9" s="59" t="s">
+        <s:v>176</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="10" ht="24.75">
+      <s:c r="A10" s="82">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="B10" s="6"/>
-      <s:c r="C10" s="6"/>
-      <s:c r="D10" s="6"/>
-      <s:c r="E10" s="6"/>
-    </s:row>
-    <s:row r="11">
-      <s:c r="A11" s="4">
+      <s:c r="B10" s="59" t="s">
+        <s:v>179</s:v>
+      </s:c>
+      <s:c r="C10" s="59"/>
+      <s:c r="D10" s="59"/>
+      <s:c r="E10" s="59" t="s">
+        <s:v>178</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="11" ht="58.5">
+      <s:c r="A11" s="82">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="B11" s="6"/>
-      <s:c r="C11" s="6"/>
-      <s:c r="D11" s="6"/>
-      <s:c r="E11" s="6"/>
-    </s:row>
-    <s:row r="12">
-      <s:c r="A12" s="4">
+      <s:c r="B11" s="59" t="s">
+        <s:v>180</s:v>
+      </s:c>
+      <s:c r="C11" s="59"/>
+      <s:c r="D11" s="59"/>
+      <s:c r="E11" s="59" t="s">
+        <s:v>181</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="12" ht="47.25">
+      <s:c r="A12" s="82">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="B12" s="6"/>
-      <s:c r="C12" s="6"/>
-      <s:c r="D12" s="6"/>
-      <s:c r="E12" s="6"/>
+      <s:c r="B12" s="59" t="s">
+        <s:v>182</s:v>
+      </s:c>
+      <s:c r="C12" s="59"/>
+      <s:c r="D12" s="59"/>
+      <s:c r="E12" s="59" t="s">
+        <s:v>184</s:v>
+      </s:c>
     </s:row>
     <s:row r="13">
       <s:c r="A13" s="4">
@@ -4820,46 +5030,46 @@
   </s:cols>
   <s:sheetData>
     <s:row r="1">
-      <s:c r="A1" s="37" t="s">
+      <s:c r="A1" s="79" t="s">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="B1" s="37" t="s">
+      <s:c r="B1" s="79" t="s">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="C1" s="37" t="s">
+      <s:c r="C1" s="79" t="s">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D1" s="37" t="s">
+      <s:c r="D1" s="79" t="s">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="E1" s="37" t="s">
+      <s:c r="E1" s="79" t="s">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="F1" s="37" t="s">
+      <s:c r="F1" s="79" t="s">
         <s:v>136</s:v>
       </s:c>
     </s:row>
     <s:row r="2" ht="110.25">
-      <s:c r="A2" s="35" t="s">
+      <s:c r="A2" s="87" t="s">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="B2" s="36" t="s">
+      <s:c r="B2" s="88" t="s">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="C2" s="36" t="s">
+      <s:c r="C2" s="88" t="s">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D2" s="35" t="s">
+      <s:c r="D2" s="87" t="s">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="E2" s="35" t="s">
+      <s:c r="E2" s="87" t="s">
         <s:v>92</s:v>
       </s:c>
-      <s:c r="F2" s="51">
+      <s:c r="F2" s="89">
         <s:v>46108</s:v>
       </s:c>
     </s:row>
-    <s:row r="3" ht="146.25">
+    <s:row r="3" ht="158.25">
       <s:c r="A3" s="35" t="s">
         <s:v>22</s:v>
       </s:c>
@@ -4873,33 +5083,33 @@
         <s:v>28</s:v>
       </s:c>
       <s:c r="E3" s="35" t="s">
-        <s:v>86</s:v>
+        <s:v>167</s:v>
       </s:c>
       <s:c r="F3" s="51">
-        <s:v>46104</s:v>
+        <s:v>46108</s:v>
       </s:c>
     </s:row>
     <s:row r="4" ht="110.25">
-      <s:c r="A4" s="35" t="s">
+      <s:c r="A4" s="76" t="s">
         <s:v>32</s:v>
       </s:c>
-      <s:c r="B4" s="35" t="s">
+      <s:c r="B4" s="76" t="s">
         <s:v>34</s:v>
       </s:c>
-      <s:c r="C4" s="35" t="s">
+      <s:c r="C4" s="76" t="s">
         <s:v>36</s:v>
       </s:c>
-      <s:c r="D4" s="35" t="s">
+      <s:c r="D4" s="76" t="s">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="E4" s="35" t="s">
+      <s:c r="E4" s="76" t="s">
         <s:v>123</s:v>
       </s:c>
-      <s:c r="F4" s="51">
-        <s:v>46104</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="5" ht="38.25">
+      <s:c r="F4" s="77">
+        <s:v>46106</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="5" ht="62.25">
       <s:c r="A5" s="35" t="s">
         <s:v>42</s:v>
       </s:c>
@@ -4913,11 +5123,11 @@
         <s:v>19</s:v>
       </s:c>
       <s:c r="E5" s="35" t="s">
-        <s:v>90</s:v>
+        <s:v>160</s:v>
       </s:c>
       <s:c r="F5" s="3"/>
     </s:row>
-    <s:row r="6" ht="26.25">
+    <s:row r="6" ht="38.25">
       <s:c r="A6" s="35" t="s">
         <s:v>43</s:v>
       </s:c>
@@ -4931,9 +5141,11 @@
         <s:v>46</s:v>
       </s:c>
       <s:c r="E6" s="35" t="s">
-        <s:v>155</s:v>
-      </s:c>
-      <s:c r="F6" s="3"/>
+        <s:v>161</s:v>
+      </s:c>
+      <s:c r="F6" s="51">
+        <s:v>46111</s:v>
+      </s:c>
       <s:c r="G6"/>
     </s:row>
     <s:row r="7" ht="62.25">
@@ -4956,7 +5168,7 @@
         <s:v>46160</s:v>
       </s:c>
     </s:row>
-    <s:row r="8" ht="98.25">
+    <s:row r="8" ht="110.25">
       <s:c r="A8" s="35" t="s">
         <s:v>95</s:v>
       </s:c>
@@ -4968,13 +5180,13 @@
       </s:c>
       <s:c r="D8" s="35"/>
       <s:c r="E8" s="35" t="s">
-        <s:v>152</s:v>
+        <s:v>162</s:v>
       </s:c>
       <s:c r="F8" s="51">
-        <s:v>46104</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="9" ht="50.25">
+        <s:v>46111</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="9" ht="62.25">
       <s:c r="A9" s="35" t="s">
         <s:v>137</s:v>
       </s:c>
@@ -4986,10 +5198,10 @@
         <s:v>101</s:v>
       </s:c>
       <s:c r="E9" s="35" t="s">
-        <s:v>151</s:v>
+        <s:v>166</s:v>
       </s:c>
       <s:c r="F9" s="51">
-        <s:v>46104</s:v>
+        <s:v>46111</s:v>
       </s:c>
     </s:row>
     <s:row r="10" ht="26.25">
@@ -5036,7 +5248,7 @@
       </s:c>
       <s:c r="F12" s="3"/>
     </s:row>
-    <s:row r="13" ht="50.25">
+    <s:row r="13" ht="86.25">
       <s:c r="A13" s="35" t="s">
         <s:v>119</s:v>
       </s:c>
@@ -5048,10 +5260,10 @@
       </s:c>
       <s:c r="D13" s="35"/>
       <s:c r="E13" s="35" t="s">
-        <s:v>149</s:v>
+        <s:v>165</s:v>
       </s:c>
       <s:c r="F13" s="51">
-        <s:v>46104</s:v>
+        <s:v>46146</s:v>
       </s:c>
     </s:row>
     <s:row r="14" ht="26.25">
@@ -5069,21 +5281,11 @@
       <s:c r="F14" s="3"/>
     </s:row>
     <s:row r="15">
-      <s:c r="A15" s="35" t="s">
-        <s:v>139</s:v>
-      </s:c>
-      <s:c r="B15" s="35">
-        <s:v>25535</s:v>
-      </s:c>
-      <s:c r="C15" s="35">
-        <s:v>57373645</s:v>
-      </s:c>
-      <s:c r="D15" s="35" t="s">
-        <s:v>158</s:v>
-      </s:c>
-      <s:c r="E15" s="35" t="s">
-        <s:v>126</s:v>
-      </s:c>
+      <s:c r="A15" s="35"/>
+      <s:c r="B15" s="35"/>
+      <s:c r="C15" s="35"/>
+      <s:c r="D15" s="35"/>
+      <s:c r="E15" s="35"/>
       <s:c r="F15" s="3"/>
     </s:row>
     <s:row r="16">

--- a/data/source.xlsx
+++ b/data/source.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<s:workbook xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<s:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <s:workbookPr/>
   <s:bookViews>
     <s:workbookView xWindow="3160" yWindow="2260" windowWidth="28240" windowHeight="17240"/>
@@ -9,8 +9,7 @@
     <s:sheet name="ДВТех" sheetId="1" state="visible" r:id="rId1"/>
     <s:sheet name="Список задач Влад" sheetId="2" state="visible" r:id="rId2"/>
     <s:sheet name="График судов" sheetId="3" state="visible" r:id="rId3"/>
-    <s:sheet name="Суды от Андрея" sheetId="4" state="visible" r:id="rId4"/>
-    <s:sheet name="Подневной план" sheetId="5" state="visible" r:id="rId5"/>
+    <s:sheet name="Вопросы Генадию" sheetId="6" state="visible" r:id="rId4"/>
   </s:sheets>
   <s:calcPr calcId="181029"/>
 </s:workbook>
@@ -674,11 +673,319 @@
   <s:si>
     <s:t>отовлю решение. Составляю осталось составить повестку дня</s:t>
   </s:si>
+  <s:si>
+    <s:t>27.02.2026 вынесено Определение первой интсанции о взыскании с ИП Флегонтова Е.А. д/с в размере  4 150 000 руб. 
+Определения опубликовано 27.02.26 срок обжалования менсяц. 
+Готовим апеляшку
+Забрать деьги с депозита суда если повторно не будем в апеляции обращаться то забираем. 
+26.03.26 Подана Апеляяционная жалоба.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>02-7002</s:t>
+  </s:si>
+  <s:si>
+    <s:t>02-0702/2026</s:t>
+  </s:si>
+  <s:si>
+    <s:t>02-0702/2026
+Хорошевский районный суд</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Гурьянова Т.А.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Приостановлено - Невозможность рассмотрения данного дела до разрешения другого в гражданском, уголовном или административном производстве, а также дела об административном правонарушении</s:t>
+  </s:si>
+  <s:si>
+    <s:t>27.02.2026 вынесено Определение первой интсанции о взыскании с ИП Флегонтова Е.А. д/с в размере  4 150 000 руб. 
+Забрать деьги с депозита суда если.
+26.03.26 Подана Апеляяционная жалоба.</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">В удовлетворении заявлени о привлечении Кидяевой А.Г. отказано.
+Ждем мотивировочную часть. Иск удовлетворен. 
+Оспаривать на основании непривлечения в качестве третьего лица. В процессе заявили ходатайство о привлечении. 
+Иск об оспаривании сделки не подавалисся. 
+Мысли: Гурьянова-Теплорост не оспорить по основаниям приемущественного права. Либо безденежность, не было денег.  
+По этому делу Кидяева обращалась к Гурьяновой и Теплорост. 
+Планировалось дождаться решения по проверке в УВД. 
+По состоянию на 27.03.2026 мотивировочной части нету </s:t>
+  </s:si>
+  <s:si>
+    <s:t>Подана апелляционная жалоба. Ждем назначения.
+1) СВО 
+2) Генадий 
+В матереалы дела предоставлены документы о доходности Гурьяновой Т.А. 
+Позиция апеляции сохраняет себя. Обращение взыскание на автовышку, автовышка была в залоге. В судже просили передать на ответ хранения отказали. Наложили залог. После решения щзаберут вышку и продадут на торгах. 
+Жалоба в суд еще не поступила</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Просят индексацию на 28 000.
+Просто отсдеживаем.
+22.01.26 от ДДС Авто поступило объяснение
+роизводство по заявлению об индексации присужденных сумм прекращено. В сявязи с пропускос срока на обращения с таким заявлением</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Возмещение по ДТП порядка 2 000 000. скостили до 300 000 по экспертизе. Во первых есть водитель с него взыскать. 
+Дождаться решения первой инстанции. Машина продана отцу истца, оценить ущерб. Они ссылась на ходовую часть автомобиля которая не подвердилась.
+04.02.26 иск удовлетворен частитчно, будем подавать апеляцию ? + отлеживаем поступление апеляшки от аппонентов.
+20.03.26 поступило ходатайство о выдачи исполнительного листа
+По состоянию на 27.03.26 АЖ не поступила</s:t>
+  </s:si>
+  <s:si>
+    <s:t>ОБ ДПС ГИБДД УВД по ЮВАО ГУ МВД России по г. Москве</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">16.03.2026 Вынесено решение о взыскании с ООО "ХардЭнерджи" 150 000 руб. 
+Ждем Решение на Гос услуги
+По состоянию на 23.03.26 Решение не опубликовано.
+27.03.2026 Опубликованно решение на сайте суда.
+Срок на обжалование 10 дней с момента получения. </s:t>
+  </s:si>
+  <s:si>
+    <s:t>Подана апелляционная жалоба. Ждем назначения.
+1) СВО 
+2) Генадий 
+В матереалы дела предоставлены документы о доходности Гурьяновой Т.А. 
+Позиция апеляции сохраняет себя. Обращение взыскание на автовышку, автовышка была в залоге. В судже просили передать на ответ хранения отказали. Наложили залог. После решения щзаберут вышку и продадут на торгах. 
+27.03.26 Жалоба в суд еще не поступила</s:t>
+  </s:si>
+  <s:si>
+    <s:t>План уничтожения Хард проекта</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">Составить план </s:t>
+  </s:si>
+  <s:si>
+    <s:t>Сделать ЭЦП ДВТех</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Напрапвить претензию Чебанаш А.В,</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Напрапвить претензию Чебанаш А.В.</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">Тюрин </s:t>
+  </s:si>
+  <s:si>
+    <s:t>Готовиться к процедуре</s:t>
+  </s:si>
+  <s:si>
+    <s:t>27.02.2026 вынесено Определение первой интсанции о взыскании с ИП Флегонтова Е.А. д/с в размере  4 150 000 руб. 
+Забрать деьги с депозита суда если.
+26.03.26 Подана Апеляяционная жалоба.
+30.03.26 жалоба поступила в суд</s:t>
+  </s:si>
+  <s:si>
+    <s:t>27.02.2026 вынесено Определение первой интсанции о взыскании с ИП Флегонтова Е.А. д/с в размере  4 150 000 руб. 
+Забрать деьги с депозита суда если.
+26.03.26 Подана Апеляяционная жалоба.
+30.03.26 жалоба поступила в суд. Ожидаем определения об оставлении без движения</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">Пусковой Элемент </s:t>
+  </s:si>
+  <s:si>
+    <s:t>+79257403343
+Самир Аль-Тамими</s:t>
+  </s:si>
+  <s:si>
+    <s:t>,</s:t>
+  </s:si>
+  <s:si>
+    <s:t>16.03.2026 Вынесено решение о взыскании с ООО "ХардЭнерджи" 150 000 руб. 
+Ждем Решение на Гос услуги.
+Срок на обжалование 10 дней с момента получения. 
+22.03.2026 получено решение по почте Росии</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">Надо поговорить с Генадием </s:t>
+  </s:si>
+  <s:si>
+    <s:t>Надо поговорить с Генадием по поводу Хард проекта</s:t>
+  </s:si>
+  <s:si>
+    <s:t>16.03.2026 Вынесено решение о взыскании с ООО "ХардЭнерджи" 150 000 руб. 
+Ждем Решение на Гос услуги.
+Срок на обжалование 10 дней с момента получения. 
+22.03.2026 получено решение по почте России.
+30.04.2026 направлена Жалоба на Решение</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Документы готовы</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Документы готовы. Осталось подписать.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Сделать печати</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">Одна в работе. Вторая нужен оттиск </s:t>
+  </s:si>
+  <s:si>
+    <s:t>Подана апелляционная жалоба. Ждем назначения.
+1) СВО 
+2) Генадий 
+В матереалы дела предоставлены документы о доходности Гурьяновой Т.А. 
+Позиция апеляции сохраняет себя. Обращение взыскание на автовышку, автовышка была в залоге. В судже просили передать на ответ хранения отказали. Наложили залог. После решения щзаберут вышку и продадут на торгах. 
+02</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Подана апелляционная жалоба. Ждем назначения.
+1) СВО 
+2) Генадий 
+В матереалы дела предоставлены документы о доходности Гурьяновой Т.А. 
+Позиция апеляции сохраняет себя. Обращение взыскание на автовышку, автовышка была в залоге. В судже просили передать на ответ хранения отказали. Наложили залог. После решения щзаберут вышку и продадут на торгах. 
+02.04.26 Жалоба поступила в суд.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>23.04.26 в 09:55</s:t>
+  </s:si>
+  <s:si>
+    <s:t>02-6420/2025
+33-16116/2026
+Хорошевский районный суд</s:t>
+  </s:si>
+  <s:si>
+    <s:t>03.04.26 Направлена претензия</s:t>
+  </s:si>
+  <s:si>
+    <s:t>27.02.2026 вынесено Определение первой интсанции о взыскании с ИП Флегонтова Е.А. д/с в размере  4 150 000 руб. 
+Забрать деьги с депозита суда если.
+26.03.26 Подана Апеляяционная жалоба.
+30.03.26 жалоба поступила в суд. АЖ оставлена без движения сроком до 27.04.26. Необходимо оплатить госпошлину и отправить сторонам.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>27.02.2026 вынесено Определение первой интсанции о взыскании с ИП Флегонтова Е.А. д/с в размере  4 150 000 руб. 
+Забрать деьги с депозита суда если.
+26.03.26 Подана Апеляяционная жалоба.
+30.03.26 жалоба поступила в суд. АЖ оставлена без движения сроком до 27.04.26. Необходимо оплатить госпошлину 30 000 и отправить сторонам.</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">В удовлетворении заявлени о привлечении Кидяевой А.Г. отказано.
+Ждем мотивировочную часть. Иск удовлетворен. 
+Оспаривать на основании непривлечения в качестве третьего лица. В процессе заявили ходатайство о привлечении. 
+Иск об оспаривании сделки не подавалисся. 
+Мысли: Гурьянова-Теплорост не оспорить по основаниям приемущественного права. Либо безденежность, не было денег.  
+По этому делу Кидяева обращалась к Гурьяновой и Теплорост. 
+Планировалось дождаться решения по проверке в УВД. 
+По состоянию на 08.04.2026 мотивировочной части нету </s:t>
+  </s:si>
+  <s:si>
+    <s:t>18.02.2026 приостановленно рассмотрение АЖ.
+Назначена экспертиза, в первой инстанции говорят что отказано, а в решении Написано что не заявлялось. 
+По состоянию на 23.03.26 заключение экспертов в суд не поступило</s:t>
+  </s:si>
+  <s:si>
+    <s:t>18.02.2026 приостановленно рассмотрение АЖ.
+Назначена экспертиза, в первой инстанции говорят что отказано, а в решении Написано что не заявлялось. 
+По состоянию на 08.04.26 заключение экспертов в суд не поступило</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">16.03.2026 Вынесено решение о взыскании с ООО "ХардЭнерджи" 150 000 руб. 
+Ждем Решение на Гос услуги.
+Срок на обжалование 10 дней с момента получения. 
+22.03.2026 получено решение по почте России.
+30.04.2026 направлена Жалоба на Решение. Согласно трекномеру жалоба в суд поступила. Ждем назначения </s:t>
+  </s:si>
+  <s:si>
+    <s:t>03.04.26 Направлена претензия.</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">03.04.26 Направлена претензия.
+08.04.2026 Оплачена задолженность </s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">Теокомтех: </s:t>
+  </s:si>
+  <s:si>
+    <s:t>- Варианты решений по аренде?</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Тюрин А.</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">Должен 15 000 000. заводим процедуру банкроства ? </s:t>
+  </s:si>
+  <s:si>
+    <s:r>
+      <s:rPr>
+        <s:vertAlign val="baseline"/>
+        <s:scheme val="minor"/>
+      </s:rPr>
+      <s:t xml:space="preserve">02-6420/2025
+</s:t>
+    </s:r>
+    <s:r>
+      <s:rPr>
+        <s:vertAlign val="baseline"/>
+        <s:scheme val="minor"/>
+      </s:rPr>
+      <s:t xml:space="preserve">33-16116/2026
+</s:t>
+    </s:r>
+    <s:r>
+      <s:rPr>
+        <s:vertAlign val="baseline"/>
+        <s:scheme val="minor"/>
+      </s:rPr>
+      <s:t>Хорошевский районный суд</s:t>
+    </s:r>
+  </s:si>
+  <s:si>
+    <s:t>23.04.26 в 09:55 сз</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ОСпорить продажу доли. </s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">Оспорить продажу доли. </s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">ХардПроект </s:t>
+  </s:si>
+  <s:si>
+    <s:t>Продать долю
+Управляющий ИП Атегов</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Камскоп</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">Продать или переформить </s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">В удовлетворении заявлени о привлечении Кидяевой А.Г. отказано.
+Ждем мотивировочную часть. Иск удовлетворен. 
+Оспаривать на основании непривлечения в качестве третьего лица. В процессе заявили ходатайство о привлечении. 
+Иск об оспаривании сделки не подавалисся. 
+Мысли: Гурьянова-Теплорост не оспорить по основаниям приемущественного права. Либо безденежность, не было денег.  
+По этому делу Кидяева обращалась к Гурьяновой и Теплорост. 
+Планировалось дождаться решения по проверке в УВД. 
+По состоянию на 13.04.2026 мотивировочной части нету </s:t>
+  </s:si>
+  <s:si>
+    <s:t>Подана апелляционная жалоба. Ждем назначения.
+1) СВО 
+2) Генадий 
+В матереалы дела предоставлены документы о доходности Гурьяновой Т.А. 
+Позиция апеляции сохраняет себя. Обращение взыскание на автовышку, автовышка была в залоге. В судже просили передать на ответ хранения отказали. Наложили залог. После решения щзаберут вышку и продадут на торгах. 
+02.04.26 Жалоба поступила в суд.
+17.04.2026 направить ходатайство сторонам и в суд</s:t>
+  </s:si>
+  <s:si>
+    <s:t>27.02.2026 вынесено Определение первой интсанции о взыскании с ИП Флегонтова Е.А. д/с в размере  4 150 000 руб. 
+Забрать деьги с депозита суда. Входящий № 8542 от 13.04.26
+26.03.26 Подана Апеляяционная жалоба.
+30.03.26 жалоба поступила в суд. АЖ оставлена без движения сроком до 27.04.26. Необходимо оплатить госпошлину 30 000 и отправить сторонам.</s:t>
+  </s:si>
 </s:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<s:styleSheet xmlns:vyd="http://volga.yandex.com/schemas/document/model" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<s:styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:vyd="http://volga.yandex.com/schemas/document/model" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <s:numFmts count="2">
     <s:numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
     <s:numFmt numFmtId="165" formatCode="dd\.mm\.yy"/>
@@ -705,7 +1012,7 @@
       <s:sz val="10"/>
     </s:font>
   </s:fonts>
-  <s:fills count="12">
+  <s:fills count="15">
     <s:fill>
       <s:patternFill patternType="none"/>
     </s:fill>
@@ -772,8 +1079,25 @@
         <s:bgColor rgb="FFFF6964"/>
       </s:patternFill>
     </s:fill>
+    <s:fill>
+      <s:patternFill patternType="solid">
+        <s:fgColor rgb="FFFFFFFF"/>
+        <s:bgColor rgb="FFFFFFFF"/>
+      </s:patternFill>
+    </s:fill>
+    <s:fill>
+      <s:patternFill patternType="solid">
+        <s:fgColor rgb="FF25BB5C"/>
+        <s:bgColor rgb="FF25BB5C"/>
+      </s:patternFill>
+    </s:fill>
+    <s:fill>
+      <s:patternFill patternType="solid">
+        <s:fgColor rgb="FFFFFFFF"/>
+      </s:patternFill>
+    </s:fill>
   </s:fills>
-  <s:borders count="14">
+  <s:borders count="15">
     <s:border>
       <s:left/>
       <s:right/>
@@ -839,11 +1163,25 @@
       <s:top/>
       <s:bottom/>
     </s:border>
+    <s:border>
+      <s:left style="none">
+        <s:color rgb="none"/>
+      </s:left>
+      <s:right style="none">
+        <s:color rgb="none"/>
+      </s:right>
+      <s:top style="none">
+        <s:color rgb="none"/>
+      </s:top>
+      <s:bottom style="none">
+        <s:color rgb="none"/>
+      </s:bottom>
+    </s:border>
   </s:borders>
   <s:cellStyleXfs count="1">
     <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </s:cellStyleXfs>
-  <s:cellXfs count="90">
+  <s:cellXfs count="105">
     <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <s:xf applyAlignment="1">
       <s:alignment vertical="center" mc:Ignorable="vyd"/>
@@ -1063,6 +1401,47 @@
     </s:xf>
     <s:xf numFmtId="165" fillId="11" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <s:alignment horizontal="center" vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fillId="12" applyFill="1"/>
+    <s:xf fontId="1" fillId="12" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="1" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="165" fillId="12" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="1" fillId="12" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fillId="13" borderId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="1" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="164" fillId="13" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="165" fillId="13" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="1" fillId="13" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="1" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="1" fillId="13" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fillId="13" borderId="1" applyFill="1" applyBorder="1"/>
+    <s:xf fontId="1" fillId="14" borderId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="0" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="1" fillId="14" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="0" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <s:alignment vertical="center" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="1" borderId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="0" vyd:clipText="0" mc:Ignorable="vyd"/>
+    </s:xf>
+    <s:xf fontId="1" borderId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <s:alignment horizontal="center" vertical="center" wrapText="0" vyd:clipText="0" mc:Ignorable="vyd"/>
     </s:xf>
   </s:cellXfs>
   <s:cellStyles count="1">
@@ -1296,18 +1675,24 @@
       <s:c r="G1" s="2"/>
     </s:row>
     <s:row r="2" ht="24.75">
-      <s:c r="A2" s="59"/>
-      <s:c r="B2" s="59" t="s">
+      <s:c r="A2" s="94">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="B2" s="94" t="s">
         <s:v>168</s:v>
       </s:c>
-      <s:c r="C2" s="60"/>
-      <s:c r="D2" s="61"/>
-      <s:c r="E2" s="59"/>
+      <s:c r="C2" s="95"/>
+      <s:c r="D2" s="96"/>
+      <s:c r="E2" s="94" t="s">
+        <s:v>217</s:v>
+      </s:c>
       <s:c r="F2" s="2"/>
       <s:c r="G2" s="2"/>
     </s:row>
     <s:row r="3" ht="24.75">
-      <s:c r="A3" s="59"/>
+      <s:c r="A3" s="59">
+        <s:v>2</s:v>
+      </s:c>
       <s:c r="B3" s="59" t="s">
         <s:v>5</s:v>
       </s:c>
@@ -1320,7 +1705,9 @@
       <s:c r="G3" s="2"/>
     </s:row>
     <s:row r="4" ht="36">
-      <s:c r="A4" s="59"/>
+      <s:c r="A4" s="59">
+        <s:v>3</s:v>
+      </s:c>
       <s:c r="B4" s="83" t="s">
         <s:v>6</s:v>
       </s:c>
@@ -1333,7 +1720,9 @@
       <s:c r="G4" s="2"/>
     </s:row>
     <s:row r="5" ht="14.25">
-      <s:c r="A5" s="6"/>
+      <s:c r="A5" s="6">
+        <s:v>4</s:v>
+      </s:c>
       <s:c r="B5" s="6"/>
       <s:c r="C5" s="14"/>
       <s:c r="D5" s="51"/>
@@ -1343,7 +1732,7 @@
     </s:row>
     <s:row r="6">
       <s:c r="A6" s="6">
-        <s:v>3</s:v>
+        <s:v>5</s:v>
       </s:c>
       <s:c r="B6" s="6"/>
       <s:c r="C6" s="3"/>
@@ -1354,7 +1743,7 @@
     </s:row>
     <s:row r="7">
       <s:c r="A7" s="6">
-        <s:v>4</s:v>
+        <s:v>6</s:v>
       </s:c>
       <s:c r="B7" s="6"/>
       <s:c r="C7" s="3"/>
@@ -1365,7 +1754,7 @@
     </s:row>
     <s:row r="8">
       <s:c r="A8" s="6">
-        <s:v>5</s:v>
+        <s:v>7</s:v>
       </s:c>
       <s:c r="B8" s="6"/>
       <s:c r="C8" s="3"/>
@@ -1376,7 +1765,7 @@
     </s:row>
     <s:row r="9" ht="12.75" customHeight="1">
       <s:c r="A9" s="6">
-        <s:v>6</s:v>
+        <s:v>8</s:v>
       </s:c>
       <s:c r="B9" s="6"/>
       <s:c r="C9" s="3"/>
@@ -1387,7 +1776,7 @@
     </s:row>
     <s:row r="10">
       <s:c r="A10" s="6">
-        <s:v>7</s:v>
+        <s:v>9</s:v>
       </s:c>
       <s:c r="B10" s="6"/>
       <s:c r="C10" s="3"/>
@@ -1398,7 +1787,7 @@
     </s:row>
     <s:row r="11">
       <s:c r="A11" s="6">
-        <s:v>8</s:v>
+        <s:v>10</s:v>
       </s:c>
       <s:c r="B11" s="6"/>
       <s:c r="C11" s="3"/>
@@ -1409,7 +1798,7 @@
     </s:row>
     <s:row r="12">
       <s:c r="A12" s="6">
-        <s:v>9</s:v>
+        <s:v>11</s:v>
       </s:c>
       <s:c r="B12" s="6"/>
       <s:c r="C12" s="3"/>
@@ -1420,7 +1809,7 @@
     </s:row>
     <s:row r="13">
       <s:c r="A13" s="6">
-        <s:v>10</s:v>
+        <s:v>12</s:v>
       </s:c>
       <s:c r="B13" s="6"/>
       <s:c r="C13" s="3"/>
@@ -1431,7 +1820,7 @@
     </s:row>
     <s:row r="14">
       <s:c r="A14" s="6">
-        <s:v>11</s:v>
+        <s:v>13</s:v>
       </s:c>
       <s:c r="B14" s="6"/>
       <s:c r="C14" s="3"/>
@@ -1442,7 +1831,7 @@
     </s:row>
     <s:row r="15">
       <s:c r="A15" s="6">
-        <s:v>12</s:v>
+        <s:v>14</s:v>
       </s:c>
       <s:c r="B15" s="6"/>
       <s:c r="C15" s="3"/>
@@ -1453,7 +1842,7 @@
     </s:row>
     <s:row r="16">
       <s:c r="A16" s="6">
-        <s:v>13</s:v>
+        <s:v>15</s:v>
       </s:c>
       <s:c r="B16" s="6"/>
       <s:c r="C16" s="3"/>
@@ -1464,7 +1853,7 @@
     </s:row>
     <s:row r="17">
       <s:c r="A17" s="6">
-        <s:v>14</s:v>
+        <s:v>16</s:v>
       </s:c>
       <s:c r="B17" s="6"/>
       <s:c r="C17" s="3"/>
@@ -1475,7 +1864,7 @@
     </s:row>
     <s:row r="18">
       <s:c r="A18" s="6">
-        <s:v>15</s:v>
+        <s:v>17</s:v>
       </s:c>
       <s:c r="B18" s="6"/>
       <s:c r="C18" s="3"/>
@@ -1486,7 +1875,7 @@
     </s:row>
     <s:row r="19">
       <s:c r="A19" s="6">
-        <s:v>16</s:v>
+        <s:v>18</s:v>
       </s:c>
       <s:c r="B19" s="6"/>
       <s:c r="C19" s="3"/>
@@ -1497,7 +1886,7 @@
     </s:row>
     <s:row r="20">
       <s:c r="A20" s="6">
-        <s:v>17</s:v>
+        <s:v>19</s:v>
       </s:c>
       <s:c r="B20" s="6"/>
       <s:c r="C20" s="3"/>
@@ -1508,7 +1897,7 @@
     </s:row>
     <s:row r="21">
       <s:c r="A21" s="6">
-        <s:v>18</s:v>
+        <s:v>20</s:v>
       </s:c>
       <s:c r="B21" s="6"/>
       <s:c r="C21" s="3"/>
@@ -1519,7 +1908,7 @@
     </s:row>
     <s:row r="22">
       <s:c r="A22" s="6">
-        <s:v>19</s:v>
+        <s:v>21</s:v>
       </s:c>
       <s:c r="B22" s="6"/>
       <s:c r="C22" s="3"/>
@@ -1530,7 +1919,7 @@
     </s:row>
     <s:row r="23">
       <s:c r="A23" s="6">
-        <s:v>20</s:v>
+        <s:v>22</s:v>
       </s:c>
       <s:c r="B23" s="6"/>
       <s:c r="C23" s="3"/>
@@ -1541,7 +1930,7 @@
     </s:row>
     <s:row r="24">
       <s:c r="A24" s="6">
-        <s:v>21</s:v>
+        <s:v>23</s:v>
       </s:c>
       <s:c r="B24" s="6"/>
       <s:c r="C24" s="3"/>
@@ -1552,7 +1941,7 @@
     </s:row>
     <s:row r="25">
       <s:c r="A25" s="6">
-        <s:v>22</s:v>
+        <s:v>24</s:v>
       </s:c>
       <s:c r="B25" s="6"/>
       <s:c r="C25" s="3"/>
@@ -1563,7 +1952,7 @@
     </s:row>
     <s:row r="26">
       <s:c r="A26" s="6">
-        <s:v>23</s:v>
+        <s:v>25</s:v>
       </s:c>
       <s:c r="B26" s="6"/>
       <s:c r="C26" s="3"/>
@@ -1574,7 +1963,7 @@
     </s:row>
     <s:row r="27">
       <s:c r="A27" s="6">
-        <s:v>24</s:v>
+        <s:v>26</s:v>
       </s:c>
       <s:c r="B27" s="6"/>
       <s:c r="C27" s="3"/>
@@ -1585,7 +1974,7 @@
     </s:row>
     <s:row r="28">
       <s:c r="A28" s="6">
-        <s:v>25</s:v>
+        <s:v>27</s:v>
       </s:c>
       <s:c r="B28" s="6"/>
       <s:c r="C28" s="3"/>
@@ -4885,41 +5274,53 @@
         <s:v>184</s:v>
       </s:c>
     </s:row>
-    <s:row r="13">
+    <s:row r="13" ht="36">
       <s:c r="A13" s="4">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="B13" s="6"/>
+      <s:c r="B13" s="6" t="s">
+        <s:v>200</s:v>
+      </s:c>
       <s:c r="C13" s="6"/>
       <s:c r="D13" s="6"/>
-      <s:c r="E13" s="6"/>
-    </s:row>
-    <s:row r="14">
-      <s:c r="A14" s="4">
+      <s:c r="E13" s="6" t="s">
+        <s:v>201</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="14" ht="24.75">
+      <s:c r="A14" s="99">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="B14" s="6"/>
-      <s:c r="C14" s="6"/>
-      <s:c r="D14" s="6"/>
-      <s:c r="E14" s="6"/>
-    </s:row>
-    <s:row r="15">
-      <s:c r="A15" s="4">
+      <s:c r="B14" s="94" t="s">
+        <s:v>202</s:v>
+      </s:c>
+      <s:c r="C14" s="94"/>
+      <s:c r="D14" s="94"/>
+      <s:c r="E14" s="94"/>
+    </s:row>
+    <s:row r="15" ht="36">
+      <s:c r="A15" s="99">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="B15" s="6"/>
-      <s:c r="C15" s="6"/>
-      <s:c r="D15" s="6"/>
-      <s:c r="E15" s="6"/>
+      <s:c r="B15" s="94" t="s">
+        <s:v>204</s:v>
+      </s:c>
+      <s:c r="C15" s="94"/>
+      <s:c r="D15" s="94"/>
+      <s:c r="E15" s="94"/>
     </s:row>
     <s:row r="16">
-      <s:c r="A16" s="4">
+      <s:c r="A16" s="99">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="B16" s="6"/>
-      <s:c r="C16" s="6"/>
-      <s:c r="D16" s="6"/>
-      <s:c r="E16" s="6"/>
+      <s:c r="B16" s="94" t="s">
+        <s:v>218</s:v>
+      </s:c>
+      <s:c r="C16" s="94"/>
+      <s:c r="D16" s="94"/>
+      <s:c r="E16" s="94" t="s">
+        <s:v>219</s:v>
+      </s:c>
     </s:row>
     <s:row r="17">
       <s:c r="A17" s="4">
@@ -5023,7 +5424,7 @@
   <s:cols>
     <s:col min="1" max="1" width="14.563" customWidth="1"/>
     <s:col min="2" max="2" width="22.793" customWidth="1"/>
-    <s:col min="3" max="3" width="28.051" customWidth="1"/>
+    <s:col min="3" max="3" width="29.672" customWidth="1"/>
     <s:col min="4" max="4" width="21.98" customWidth="1"/>
     <s:col min="5" max="5" width="48.293" customWidth="1"/>
     <s:col min="6" max="6" width="10.922" style="2" customWidth="1"/>
@@ -5049,24 +5450,24 @@
         <s:v>136</s:v>
       </s:c>
     </s:row>
-    <s:row r="2" ht="110.25">
-      <s:c r="A2" s="87" t="s">
+    <s:row r="2" ht="98.25">
+      <s:c r="A2" s="91" t="s">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="B2" s="88" t="s">
+      <s:c r="B2" s="93" t="s">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="C2" s="88" t="s">
+      <s:c r="C2" s="93" t="s">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D2" s="87" t="s">
+      <s:c r="D2" s="91" t="s">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="E2" s="87" t="s">
-        <s:v>92</s:v>
-      </s:c>
-      <s:c r="F2" s="89">
-        <s:v>46108</s:v>
+      <s:c r="E2" s="91" t="s">
+        <s:v>247</s:v>
+      </s:c>
+      <s:c r="F2" s="92">
+        <s:v>46138</s:v>
       </s:c>
     </s:row>
     <s:row r="3" ht="158.25">
@@ -5083,209 +5484,217 @@
         <s:v>28</s:v>
       </s:c>
       <s:c r="E3" s="35" t="s">
-        <s:v>167</s:v>
+        <s:v>245</s:v>
       </s:c>
       <s:c r="F3" s="51">
-        <s:v>46108</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="4" ht="110.25">
-      <s:c r="A4" s="76" t="s">
-        <s:v>32</s:v>
-      </s:c>
-      <s:c r="B4" s="76" t="s">
+        <s:v>46111</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="4" ht="134.25">
+      <s:c r="A4" s="91" t="s">
+        <s:v>223</s:v>
+      </s:c>
+      <s:c r="B4" s="91" t="s">
         <s:v>34</s:v>
       </s:c>
-      <s:c r="C4" s="76" t="s">
+      <s:c r="C4" s="91" t="s">
         <s:v>36</s:v>
       </s:c>
-      <s:c r="D4" s="76" t="s">
+      <s:c r="D4" s="91" t="s">
+        <s:v>222</s:v>
+      </s:c>
+      <s:c r="E4" s="91" t="s">
+        <s:v>246</s:v>
+      </s:c>
+      <s:c r="F4" s="92">
+        <s:v>46129</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="5" s="90" customFormat="1" ht="50.25">
+      <s:c r="A5" s="91" t="s">
+        <s:v>189</s:v>
+      </s:c>
+      <s:c r="B5" s="91" t="s">
+        <s:v>190</s:v>
+      </s:c>
+      <s:c r="C5" s="91" t="s">
+        <s:v>36</s:v>
+      </s:c>
+      <s:c r="D5" s="91" t="s">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="E4" s="76" t="s">
-        <s:v>123</s:v>
-      </s:c>
-      <s:c r="F4" s="77">
-        <s:v>46106</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="5" ht="62.25">
-      <s:c r="A5" s="35" t="s">
+      <s:c r="E5" s="91" t="s">
+        <s:v>191</s:v>
+      </s:c>
+      <s:c r="F5" s="92"/>
+    </s:row>
+    <s:row r="6" ht="62.25">
+      <s:c r="A6" s="35" t="s">
         <s:v>42</s:v>
       </s:c>
-      <s:c r="B5" s="35" t="s">
+      <s:c r="B6" s="35" t="s">
         <s:v>39</s:v>
       </s:c>
-      <s:c r="C5" s="35" t="s">
+      <s:c r="C6" s="35" t="s">
         <s:v>40</s:v>
       </s:c>
-      <s:c r="D5" s="35" t="s">
+      <s:c r="D6" s="35" t="s">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="E5" s="35" t="s">
-        <s:v>160</s:v>
-      </s:c>
-      <s:c r="F5" s="3"/>
-    </s:row>
-    <s:row r="6" ht="38.25">
-      <s:c r="A6" s="35" t="s">
+      <s:c r="E6" s="35" t="s">
+        <s:v>229</s:v>
+      </s:c>
+      <s:c r="F6" s="3"/>
+    </s:row>
+    <s:row r="7" ht="74.25">
+      <s:c r="A7" s="35" t="s">
         <s:v>43</s:v>
       </s:c>
-      <s:c r="B6" s="35" t="s">
+      <s:c r="B7" s="35" t="s">
         <s:v>44</s:v>
-      </s:c>
-      <s:c r="C6" s="35" t="s">
-        <s:v>45</s:v>
-      </s:c>
-      <s:c r="D6" s="35" t="s">
-        <s:v>46</s:v>
-      </s:c>
-      <s:c r="E6" s="35" t="s">
-        <s:v>161</s:v>
-      </s:c>
-      <s:c r="F6" s="51">
-        <s:v>46111</s:v>
-      </s:c>
-      <s:c r="G6"/>
-    </s:row>
-    <s:row r="7" ht="62.25">
-      <s:c r="A7" s="35" t="s">
-        <s:v>70</s:v>
-      </s:c>
-      <s:c r="B7" s="35" t="s">
-        <s:v>72</s:v>
       </s:c>
       <s:c r="C7" s="35" t="s">
         <s:v>45</s:v>
       </s:c>
-      <s:c r="D7" s="35" t="s">
-        <s:v>135</s:v>
-      </s:c>
+      <s:c r="D7" s="35"/>
       <s:c r="E7" s="35" t="s">
-        <s:v>76</s:v>
-      </s:c>
-      <s:c r="F7" s="51">
-        <s:v>46160</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="8" ht="110.25">
+        <s:v>195</s:v>
+      </s:c>
+      <s:c r="F7" s="51"/>
+      <s:c r="G7"/>
+    </s:row>
+    <s:row r="8" ht="62.25">
       <s:c r="A8" s="35" t="s">
-        <s:v>95</s:v>
+        <s:v>70</s:v>
       </s:c>
       <s:c r="B8" s="35" t="s">
-        <s:v>96</s:v>
+        <s:v>72</s:v>
       </s:c>
       <s:c r="C8" s="35" t="s">
         <s:v>45</s:v>
       </s:c>
-      <s:c r="D8" s="35"/>
+      <s:c r="D8" s="35" t="s">
+        <s:v>135</s:v>
+      </s:c>
       <s:c r="E8" s="35" t="s">
-        <s:v>162</s:v>
+        <s:v>76</s:v>
       </s:c>
       <s:c r="F8" s="51">
-        <s:v>46111</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="9" ht="62.25">
+        <s:v>46160</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="9" ht="134.25">
       <s:c r="A9" s="35" t="s">
-        <s:v>137</s:v>
+        <s:v>95</s:v>
       </s:c>
       <s:c r="B9" s="35" t="s">
+        <s:v>96</s:v>
+      </s:c>
+      <s:c r="C9" s="35" t="s">
         <s:v>45</s:v>
       </s:c>
-      <s:c r="C9" s="35"/>
-      <s:c r="D9" s="50" t="s">
-        <s:v>101</s:v>
-      </s:c>
+      <s:c r="D9" s="35"/>
       <s:c r="E9" s="35" t="s">
-        <s:v>166</s:v>
+        <s:v>196</s:v>
       </s:c>
       <s:c r="F9" s="51">
         <s:v>46111</s:v>
       </s:c>
     </s:row>
-    <s:row r="10" ht="26.25">
+    <s:row r="10" ht="86.25">
       <s:c r="A10" s="35" t="s">
-        <s:v>106</s:v>
+        <s:v>137</s:v>
       </s:c>
       <s:c r="B10" s="35" t="s">
         <s:v>45</s:v>
       </s:c>
       <s:c r="C10" s="35" t="s">
+        <s:v>197</s:v>
+      </s:c>
+      <s:c r="D10" s="50" t="s">
+        <s:v>101</s:v>
+      </s:c>
+      <s:c r="E10" s="35" t="s">
+        <s:v>230</s:v>
+      </s:c>
+      <s:c r="F10" s="51">
+        <s:v>46115</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="11" ht="26.25">
+      <s:c r="A11" s="35" t="s">
+        <s:v>106</s:v>
+      </s:c>
+      <s:c r="B11" s="35" t="s">
+        <s:v>45</s:v>
+      </s:c>
+      <s:c r="C11" s="35" t="s">
         <s:v>112</s:v>
       </s:c>
-      <s:c r="D10" s="35" t="s">
+      <s:c r="D11" s="35" t="s">
         <s:v>109</s:v>
       </s:c>
-      <s:c r="E10" s="35" t="s">
+      <s:c r="E11" s="35" t="s">
         <s:v>111</s:v>
       </s:c>
-      <s:c r="F10" s="51">
-        <s:v>46111</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="11">
-      <s:c r="A11" s="35"/>
-      <s:c r="B11" s="35" t="s">
-        <s:v>114</s:v>
-      </s:c>
-      <s:c r="C11" s="35"/>
-      <s:c r="D11" s="35"/>
-      <s:c r="E11" s="35" t="s">
-        <s:v>118</s:v>
-      </s:c>
-      <s:c r="F11" s="3"/>
+      <s:c r="F11" s="51">
+        <s:v>46113</s:v>
+      </s:c>
     </s:row>
     <s:row r="12">
       <s:c r="A12" s="35"/>
       <s:c r="B12" s="35" t="s">
-        <s:v>115</s:v>
+        <s:v>114</s:v>
       </s:c>
       <s:c r="C12" s="35"/>
       <s:c r="D12" s="35"/>
       <s:c r="E12" s="35" t="s">
-        <s:v>117</s:v>
+        <s:v>118</s:v>
       </s:c>
       <s:c r="F12" s="3"/>
     </s:row>
-    <s:row r="13" ht="86.25">
-      <s:c r="A13" s="35" t="s">
-        <s:v>119</s:v>
-      </s:c>
+    <s:row r="13">
+      <s:c r="A13" s="35"/>
       <s:c r="B13" s="35" t="s">
-        <s:v>122</s:v>
-      </s:c>
-      <s:c r="C13" s="35" t="s">
-        <s:v>45</s:v>
-      </s:c>
+        <s:v>115</s:v>
+      </s:c>
+      <s:c r="C13" s="35"/>
       <s:c r="D13" s="35"/>
       <s:c r="E13" s="35" t="s">
-        <s:v>165</s:v>
-      </s:c>
-      <s:c r="F13" s="51">
-        <s:v>46146</s:v>
-      </s:c>
-    </s:row>
-    <s:row r="14" ht="26.25">
-      <s:c r="A14" s="35"/>
+        <s:v>117</s:v>
+      </s:c>
+      <s:c r="F13" s="3"/>
+    </s:row>
+    <s:row r="14" ht="86.25">
+      <s:c r="A14" s="35" t="s">
+        <s:v>119</s:v>
+      </s:c>
       <s:c r="B14" s="35" t="s">
+        <s:v>122</s:v>
+      </s:c>
+      <s:c r="C14" s="35" t="s">
         <s:v>45</s:v>
-      </s:c>
-      <s:c r="C14" s="35" t="s">
-        <s:v>124</s:v>
       </s:c>
       <s:c r="D14" s="35"/>
       <s:c r="E14" s="35" t="s">
+        <s:v>165</s:v>
+      </s:c>
+      <s:c r="F14" s="51">
+        <s:v>46146</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="15" ht="26.25">
+      <s:c r="A15" s="35"/>
+      <s:c r="B15" s="35" t="s">
+        <s:v>45</s:v>
+      </s:c>
+      <s:c r="C15" s="35" t="s">
+        <s:v>124</s:v>
+      </s:c>
+      <s:c r="D15" s="35"/>
+      <s:c r="E15" s="35" t="s">
         <s:v>154</s:v>
       </s:c>
-      <s:c r="F14" s="3"/>
-    </s:row>
-    <s:row r="15">
-      <s:c r="A15" s="35"/>
-      <s:c r="B15" s="35"/>
-      <s:c r="C15" s="35"/>
-      <s:c r="D15" s="35"/>
-      <s:c r="E15" s="35"/>
       <s:c r="F15" s="3"/>
     </s:row>
     <s:row r="16">
@@ -5408,87 +5817,100 @@
       <s:c r="E30" s="35"/>
       <s:c r="F30" s="3"/>
     </s:row>
-    <s:row r="31">
-      <s:c r="A31" s="35"/>
+    <s:row r="31" ht="50.25">
+      <s:c r="A31" s="35" t="s">
+        <s:v>214</s:v>
+      </s:c>
       <s:c r="B31" s="35"/>
       <s:c r="C31" s="35"/>
       <s:c r="D31" s="35"/>
       <s:c r="E31" s="35"/>
       <s:c r="F31" s="3"/>
     </s:row>
-    <s:row r="38">
-      <s:c r="A38" s="40" t="s">
+    <s:row r="32">
+      <s:c r="A32" s="35"/>
+      <s:c r="B32" s="35"/>
+      <s:c r="C32" s="35"/>
+      <s:c r="D32" s="35"/>
+      <s:c r="E32" s="35"/>
+      <s:c r="F32" s="3"/>
+    </s:row>
+    <s:row r="39">
+      <s:c r="A39" s="40" t="s">
         <s:v>49</s:v>
       </s:c>
-      <s:c r="B38" s="41"/>
-      <s:c r="C38" s="41"/>
-      <s:c r="D38" s="46"/>
-      <s:c r="E38" s="46"/>
-    </s:row>
-    <s:row r="39">
-      <s:c r="A39" s="37" t="s">
+      <s:c r="B39" s="41"/>
+      <s:c r="C39" s="41"/>
+      <s:c r="D39" s="46"/>
+      <s:c r="E39" s="46"/>
+    </s:row>
+    <s:row r="40">
+      <s:c r="A40" s="37" t="s">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="B39" s="37" t="s">
+      <s:c r="B40" s="37" t="s">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="C39" s="37" t="s">
+      <s:c r="C40" s="37" t="s">
         <s:v>4</s:v>
-      </s:c>
-      <s:c r="D39" s="48"/>
-      <s:c r="E39" s="48"/>
-    </s:row>
-    <s:row r="40" ht="26.25">
-      <s:c r="A40" s="35" t="s">
-        <s:v>45</s:v>
-      </s:c>
-      <s:c r="B40" s="36" t="s">
-        <s:v>52</s:v>
-      </s:c>
-      <s:c r="C40" s="36" t="s">
-        <s:v>54</s:v>
       </s:c>
       <s:c r="D40" s="48"/>
       <s:c r="E40" s="48"/>
     </s:row>
-    <s:row r="41">
-      <s:c r="A41" s="35" t="s">
+    <s:row r="41" ht="26.25">
+      <s:c r="A41" s="97" t="s">
         <s:v>45</s:v>
       </s:c>
-      <s:c r="B41" s="36" t="s">
-        <s:v>56</s:v>
-      </s:c>
-      <s:c r="C41" s="36" t="s">
-        <s:v>55</s:v>
+      <s:c r="B41" s="98" t="s">
+        <s:v>52</s:v>
+      </s:c>
+      <s:c r="C41" s="98" t="s">
+        <s:v>232</s:v>
       </s:c>
       <s:c r="D41" s="48"/>
       <s:c r="E41" s="48"/>
     </s:row>
-    <s:row r="42" ht="26.25">
-      <s:c r="A42" s="36" t="s">
+    <s:row r="42">
+      <s:c r="A42" s="35" t="s">
+        <s:v>45</s:v>
+      </s:c>
+      <s:c r="B42" s="36" t="s">
+        <s:v>56</s:v>
+      </s:c>
+      <s:c r="C42" s="36" t="s">
+        <s:v>55</s:v>
+      </s:c>
+      <s:c r="D42" s="48"/>
+      <s:c r="E42" s="48"/>
+    </s:row>
+    <s:row r="43" ht="26.25">
+      <s:c r="A43" s="36" t="s">
         <s:v>36</s:v>
       </s:c>
-      <s:c r="B42" s="36" t="s">
+      <s:c r="B43" s="36" t="s">
         <s:v>144</s:v>
       </s:c>
-      <s:c r="C42" s="36" t="s">
+      <s:c r="C43" s="36" t="s">
         <s:v>148</s:v>
       </s:c>
-    </s:row>
-    <s:row r="43">
-      <s:c r="A43" s="36"/>
-      <s:c r="B43" s="36"/>
-      <s:c r="C43" s="36"/>
     </s:row>
     <s:row r="44">
       <s:c r="A44" s="36"/>
-      <s:c r="B44" s="36"/>
-      <s:c r="C44" s="36"/>
-    </s:row>
-    <s:row r="45">
+      <s:c r="B44" s="36" t="s">
+        <s:v>235</s:v>
+      </s:c>
+      <s:c r="C44" s="36" t="s">
+        <s:v>206</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="45" ht="26.25">
       <s:c r="A45" s="36"/>
-      <s:c r="B45" s="36"/>
-      <s:c r="C45" s="36"/>
+      <s:c r="B45" s="36" t="s">
+        <s:v>209</s:v>
+      </s:c>
+      <s:c r="C45" s="36" t="s">
+        <s:v>210</s:v>
+      </s:c>
     </s:row>
     <s:row r="46">
       <s:c r="A46" s="36"/>
@@ -5530,27 +5952,32 @@
       <s:c r="B53" s="36"/>
       <s:c r="C53" s="36"/>
     </s:row>
-    <s:row r="56">
-      <s:c r="A56" t="s">
+    <s:row r="54">
+      <s:c r="A54" s="36"/>
+      <s:c r="B54" s="36"/>
+      <s:c r="C54" s="36"/>
+    </s:row>
+    <s:row r="57">
+      <s:c r="A57" t="s">
         <s:v>68</s:v>
       </s:c>
     </s:row>
-    <s:row r="64" ht="36">
-      <s:c r="C64" t="s">
+    <s:row r="65" ht="36">
+      <s:c r="C65" t="s">
         <s:v>64</s:v>
       </s:c>
     </s:row>
-    <s:row r="76" ht="24.75">
-      <s:c r="C76" t="s">
+    <s:row r="77" ht="24.75">
+      <s:c r="C77" t="s">
         <s:v>65</s:v>
       </s:c>
     </s:row>
-    <s:row r="77">
-      <s:c r="C77"/>
+    <s:row r="78">
+      <s:c r="C78"/>
     </s:row>
   </s:sheetData>
   <s:mergeCells count="1">
-    <s:mergeCell ref="A38:C38"/>
+    <s:mergeCell ref="A39:C39"/>
   </s:mergeCells>
 </s:worksheet>
 </file>
@@ -5560,26 +5987,94 @@
   <s:sheetPr/>
   <s:dimension ref="A1"/>
   <s:sheetFormatPr baseColWidth="13" defaultColWidth="13.4" defaultRowHeight="14.25" customHeight="1"/>
+  <s:cols>
+    <s:col min="1" max="1" width="21.98" customWidth="1"/>
+    <s:col min="2" max="2" width="25.891" style="23" customWidth="1"/>
+    <s:col min="3" max="3" width="18.754" style="23" customWidth="1"/>
+    <s:col min="4" max="4" width="30.621" customWidth="1"/>
+    <s:col min="5" max="5" width="16.594" customWidth="1"/>
+  </s:cols>
   <s:sheetData>
-    <s:row r="1">
-      <s:c r="A1" t="s">
-        <s:v>77</s:v>
-      </s:c>
+    <s:row r="1" ht="50.25">
+      <s:c r="A1" s="91" t="s">
+        <s:v>237</s:v>
+      </s:c>
+      <s:c r="B1" s="91" t="s">
+        <s:v>34</s:v>
+      </s:c>
+      <s:c r="C1" s="91" t="s">
+        <s:v>36</s:v>
+      </s:c>
+      <s:c r="D1" s="91" t="s">
+        <s:v>238</s:v>
+      </s:c>
+      <s:c r="E1" s="93"/>
     </s:row>
     <s:row r="2">
-      <s:c r="A2" t="s">
-        <s:v>81</s:v>
-      </s:c>
+      <s:c r="A2" s="104" t="s">
+        <s:v>22</s:v>
+      </s:c>
+      <s:c r="B2" s="104" t="s">
+        <s:v>24</s:v>
+      </s:c>
+      <s:c r="C2" s="104" t="s">
+        <s:v>26</s:v>
+      </s:c>
+      <s:c r="D2" s="93" t="s">
+        <s:v>240</s:v>
+      </s:c>
+      <s:c r="E2" s="93"/>
+    </s:row>
+    <s:row r="3">
+      <s:c r="A3" s="91" t="s">
+        <s:v>16</s:v>
+      </s:c>
+      <s:c r="B3" s="93" t="s">
+        <s:v>15</s:v>
+      </s:c>
+      <s:c r="C3" s="93" t="s">
+        <s:v>18</s:v>
+      </s:c>
+      <s:c r="D3" s="93" t="s">
+        <s:v>234</s:v>
+      </s:c>
+      <s:c r="E3" s="93"/>
+    </s:row>
+    <s:row r="4" ht="26.25">
+      <s:c r="A4" s="91"/>
+      <s:c r="B4" s="93" t="s">
+        <s:v>36</s:v>
+      </s:c>
+      <s:c r="C4" s="93" t="s">
+        <s:v>235</s:v>
+      </s:c>
+      <s:c r="D4" s="91" t="s">
+        <s:v>236</s:v>
+      </s:c>
+      <s:c r="E4" s="4"/>
+    </s:row>
+    <s:row r="5">
+      <s:c r="A5" s="91"/>
+      <s:c r="B5" s="91"/>
+      <s:c r="C5" s="91" t="s">
+        <s:v>241</s:v>
+      </s:c>
+      <s:c r="D5" s="91" t="s">
+        <s:v>242</s:v>
+      </s:c>
+      <s:c r="E5" s="91"/>
+    </s:row>
+    <s:row r="6">
+      <s:c r="A6" s="91"/>
+      <s:c r="B6" s="91"/>
+      <s:c r="C6" s="91" t="s">
+        <s:v>243</s:v>
+      </s:c>
+      <s:c r="D6" s="91" t="s">
+        <s:v>244</s:v>
+      </s:c>
+      <s:c r="E6" s="4"/>
     </s:row>
   </s:sheetData>
 </s:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <s:sheetPr/>
-  <s:dimension ref="A1"/>
-  <s:sheetFormatPr baseColWidth="13" defaultColWidth="13.4" defaultRowHeight="14.25" customHeight="1"/>
-  <s:sheetData/>
-</s:worksheet>
 </file>
--- a/data/source.xlsx
+++ b/data/source.xlsx
@@ -980,6 +980,42 @@
 Забрать деьги с депозита суда. Входящий № 8542 от 13.04.26
 26.03.26 Подана Апеляяционная жалоба.
 30.03.26 жалоба поступила в суд. АЖ оставлена без движения сроком до 27.04.26. Необходимо оплатить госпошлину 30 000 и отправить сторонам.</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Возмещение по ДТП порядка 2 000 000. скостили до 300 000 по экспертизе. Во первых есть водитель с него взыскать. 
+Дождаться решения первой инстанции. Машина продана отцу истца, оценить ущерб. Они ссылась на ходовую часть автомобиля которая не подвердилась.
+04.02.26 иск удовлетворен частитчно, будем подавать апеляцию ? + отлеживаем поступление апеляшки от аппонентов.
+20.03.26 поступило ходатайство о выдачи исполнительного листа
+По состоянию на 27.03.26 АЖ не поступила
+оюжалование до 20.04.26</s:t>
+  </s:si>
+  <s:si>
+    <s:t xml:space="preserve">Возмещение по ДТП порядка 2 000 000. скостили до 300 000 по экспертизе. Во первых есть водитель с него взыскать. 
+Дождаться решения первой инстанции. Машина продана отцу истца, оценить ущерб. Они ссылась на ходовую часть автомобиля которая не подвердилась.
+04.02.26 иск удовлетворен частитчно, будем подавать апеляцию ? + отлеживаем поступление апеляшки от аппонентов.
+20.03.26 поступило ходатайство о выдачи исполнительного листа
+По состоянию на 27.03.26 АЖ не поступила
+оюжалование до 20.04.26
+Был водитель который совершил ДТП за пределами уже рабочего времени. Суд первой инстанции Не дал дожной оценки настоящего довода. </s:t>
+  </s:si>
+  <s:si>
+    <s:t>Возмещение по ДТП порядка 2 000 000. скостили до 300 000 по экспертизе. Во первых есть водитель с него взыскать. 
+Дождаться решения первой инстанции. Машина продана отцу истца, оценить ущерб. Они ссылась на ходовую часть автомобиля которая не подвердилась.
+04.02.26 иск удовлетворен частитчно, будем подавать апеляцию ? + отлеживаем поступление апеляшки от аппонентов.
+20.03.26 поступило ходатайство о выдачи исполнительного листа
+По состоянию на 27.03.26 АЖ не поступила
+оюжалование до 20.04.26
+Был водитель который совершил ДТП за пределами уже рабочего времени. Суд первой инстанции Не дал дожной оценки настоящего довода. 
+На момент экспертизы машина была продана отцу или ротсвеннику. Однако машину не предоставили. Уклонился не сам истец а третье лицо</s:t>
+  </s:si>
+  <s:si>
+    <s:t>Приостановлено - Невозможность рассмотрения данного дела до разрешения другого в гражданском, уголовном или административном производстве, а также дела об административном правонарушении
+По состоянию на 20.04.2026 сз не назначено</s:t>
+  </s:si>
+  <s:si>
+    <s:t>18.02.2026 приостановленно рассмотрение АЖ.
+Назначена экспертиза, в первой инстанции говорят что отказано, а в решении Написано что не заявлялось. 
+По состоянию на 20.04.26 заключение экспертов в суд не поступило</s:t>
   </s:si>
 </s:sst>
 </file>
@@ -5510,7 +5546,7 @@
         <s:v>46129</s:v>
       </s:c>
     </s:row>
-    <s:row r="5" s="90" customFormat="1" ht="50.25">
+    <s:row r="5" s="90" customFormat="1" ht="54">
       <s:c r="A5" s="91" t="s">
         <s:v>189</s:v>
       </s:c>
@@ -5524,11 +5560,11 @@
         <s:v>19</s:v>
       </s:c>
       <s:c r="E5" s="91" t="s">
-        <s:v>191</s:v>
+        <s:v>251</s:v>
       </s:c>
       <s:c r="F5" s="92"/>
     </s:row>
-    <s:row r="6" ht="62.25">
+    <s:row r="6" ht="54">
       <s:c r="A6" s="35" t="s">
         <s:v>42</s:v>
       </s:c>
@@ -5542,7 +5578,7 @@
         <s:v>19</s:v>
       </s:c>
       <s:c r="E6" s="35" t="s">
-        <s:v>229</s:v>
+        <s:v>252</s:v>
       </s:c>
       <s:c r="F6" s="3"/>
     </s:row>
@@ -5583,22 +5619,22 @@
         <s:v>46160</s:v>
       </s:c>
     </s:row>
-    <s:row r="9" ht="134.25">
-      <s:c r="A9" s="35" t="s">
+    <s:row r="9" ht="218.25">
+      <s:c r="A9" s="91" t="s">
         <s:v>95</s:v>
       </s:c>
-      <s:c r="B9" s="35" t="s">
+      <s:c r="B9" s="91" t="s">
         <s:v>96</s:v>
       </s:c>
-      <s:c r="C9" s="35" t="s">
+      <s:c r="C9" s="91" t="s">
         <s:v>45</s:v>
       </s:c>
-      <s:c r="D9" s="35"/>
-      <s:c r="E9" s="35" t="s">
-        <s:v>196</s:v>
-      </s:c>
-      <s:c r="F9" s="51">
-        <s:v>46111</s:v>
+      <s:c r="D9" s="91"/>
+      <s:c r="E9" s="91" t="s">
+        <s:v>250</s:v>
+      </s:c>
+      <s:c r="F9" s="92">
+        <s:v>46132</s:v>
       </s:c>
     </s:row>
     <s:row r="10" ht="86.25">
@@ -5666,20 +5702,20 @@
       <s:c r="F13" s="3"/>
     </s:row>
     <s:row r="14" ht="86.25">
-      <s:c r="A14" s="35" t="s">
+      <s:c r="A14" s="76" t="s">
         <s:v>119</s:v>
       </s:c>
-      <s:c r="B14" s="35" t="s">
+      <s:c r="B14" s="76" t="s">
         <s:v>122</s:v>
       </s:c>
-      <s:c r="C14" s="35" t="s">
+      <s:c r="C14" s="76" t="s">
         <s:v>45</s:v>
       </s:c>
-      <s:c r="D14" s="35"/>
-      <s:c r="E14" s="35" t="s">
+      <s:c r="D14" s="76"/>
+      <s:c r="E14" s="76" t="s">
         <s:v>165</s:v>
       </s:c>
-      <s:c r="F14" s="51">
+      <s:c r="F14" s="77">
         <s:v>46146</s:v>
       </s:c>
     </s:row>
